--- a/public/exports-from-60/29189838.xlsx
+++ b/public/exports-from-60/29189838.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -13916,17 +13916,17 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jels Søndergade 17A</t>
+          <t xml:space="preserve">Højmarksvej 18B</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t xml:space="preserve">6630</t>
+          <t xml:space="preserve">6670</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t xml:space="preserve">5185936</t>
+          <t xml:space="preserve">8894116</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -13935,21 +13935,21 @@
         </is>
       </c>
       <c r="J186">
-        <v>270</v>
+        <v>589</v>
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t xml:space="preserve">311281954</t>
+          <t xml:space="preserve">311285343</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
         </is>
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-02</t>
+          <t xml:space="preserve">2027-11-23</t>
         </is>
       </c>
       <c r="N186" t="inlineStr">
@@ -13991,17 +13991,17 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Højmarksvej 18B</t>
+          <t xml:space="preserve">Skolegade 1B</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t xml:space="preserve">6670</t>
+          <t xml:space="preserve">6630</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t xml:space="preserve">8894116</t>
+          <t xml:space="preserve">5195702</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -14010,21 +14010,21 @@
         </is>
       </c>
       <c r="J187">
-        <v>589</v>
+        <v>695</v>
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t xml:space="preserve">311285343</t>
+          <t xml:space="preserve">311286934</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-23</t>
+          <t xml:space="preserve">2027-12-03</t>
         </is>
       </c>
       <c r="N187" t="inlineStr">
@@ -14066,7 +14066,7 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 1B</t>
+          <t xml:space="preserve">Nordre Industrivej 20</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
@@ -14076,7 +14076,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t xml:space="preserve">5195702</t>
+          <t xml:space="preserve">5198440</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -14085,21 +14085,21 @@
         </is>
       </c>
       <c r="J188">
-        <v>695</v>
+        <v>721</v>
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286934</t>
+          <t xml:space="preserve">311287623</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
         </is>
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-03</t>
+          <t xml:space="preserve">2027-12-07</t>
         </is>
       </c>
       <c r="N188" t="inlineStr">
@@ -14141,17 +14141,17 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nordre Industrivej 20</t>
+          <t xml:space="preserve">Maltvej 58</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t xml:space="preserve">6630</t>
+          <t xml:space="preserve">6600</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t xml:space="preserve">5198440</t>
+          <t xml:space="preserve">5039208</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -14160,11 +14160,11 @@
         </is>
       </c>
       <c r="J189">
-        <v>721</v>
+        <v>3216</v>
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t xml:space="preserve">311287623</t>
+          <t xml:space="preserve">311288120</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
@@ -14174,7 +14174,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-07</t>
+          <t xml:space="preserve">2027-12-11</t>
         </is>
       </c>
       <c r="N189" t="inlineStr">
@@ -14216,17 +14216,17 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t xml:space="preserve">Maltvej 58</t>
+          <t xml:space="preserve">Møllevænget 3</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t xml:space="preserve">6600</t>
+          <t xml:space="preserve">6622</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t xml:space="preserve">5039208</t>
+          <t xml:space="preserve">5019884</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -14235,11 +14235,11 @@
         </is>
       </c>
       <c r="J190">
-        <v>3216</v>
+        <v>442</v>
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t xml:space="preserve">311288120</t>
+          <t xml:space="preserve">311288925</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
@@ -14249,7 +14249,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-11</t>
+          <t xml:space="preserve">2027-12-15</t>
         </is>
       </c>
       <c r="N190" t="inlineStr">
@@ -14291,30 +14291,30 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møllevænget 3</t>
+          <t xml:space="preserve">Bakkevej 26</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t xml:space="preserve">6622</t>
+          <t xml:space="preserve">6600</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t xml:space="preserve">5019884</t>
+          <t xml:space="preserve">8097595</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J191">
-        <v>442</v>
+        <v>1538</v>
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t xml:space="preserve">311288925</t>
+          <t xml:space="preserve">311289326</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
@@ -14324,7 +14324,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-15</t>
+          <t xml:space="preserve">2027-12-18</t>
         </is>
       </c>
       <c r="N191" t="inlineStr">
@@ -14381,11 +14381,11 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J192">
-        <v>1538</v>
+        <v>2669</v>
       </c>
       <c r="K192" t="inlineStr">
         <is>
@@ -14441,7 +14441,7 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bakkevej 26</t>
+          <t xml:space="preserve">Kærdalen 1</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
@@ -14456,11 +14456,11 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J193">
-        <v>2669</v>
+        <v>1683</v>
       </c>
       <c r="K193" t="inlineStr">
         <is>
@@ -14526,20 +14526,20 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t xml:space="preserve">8097595</t>
+          <t xml:space="preserve">8097596</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J194">
-        <v>1683</v>
+        <v>1087</v>
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289326</t>
+          <t xml:space="preserve">311289816</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
@@ -14549,7 +14549,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-18</t>
+          <t xml:space="preserve">2027-12-20</t>
         </is>
       </c>
       <c r="N194" t="inlineStr">
@@ -14601,7 +14601,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t xml:space="preserve">8097596</t>
+          <t xml:space="preserve">8097597</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -14610,11 +14610,11 @@
         </is>
       </c>
       <c r="J195">
-        <v>1087</v>
+        <v>1367</v>
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289816</t>
+          <t xml:space="preserve">311289821</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
@@ -14666,17 +14666,17 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kærdalen 1</t>
+          <t xml:space="preserve">Vestergade 10</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t xml:space="preserve">6600</t>
+          <t xml:space="preserve">6622</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t xml:space="preserve">8097597</t>
+          <t xml:space="preserve">9197501</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -14685,11 +14685,11 @@
         </is>
       </c>
       <c r="J196">
-        <v>1367</v>
+        <v>706</v>
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289821</t>
+          <t xml:space="preserve">311290487</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
@@ -14699,7 +14699,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-20</t>
+          <t xml:space="preserve">2027-12-23</t>
         </is>
       </c>
       <c r="N196" t="inlineStr">
@@ -14756,11 +14756,11 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="J197">
-        <v>706</v>
+        <v>1125</v>
       </c>
       <c r="K197" t="inlineStr">
         <is>
@@ -14831,11 +14831,11 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="J198">
-        <v>1125</v>
+        <v>1045</v>
       </c>
       <c r="K198" t="inlineStr">
         <is>
@@ -14906,11 +14906,11 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="J199">
-        <v>1045</v>
+        <v>1150</v>
       </c>
       <c r="K199" t="inlineStr">
         <is>
@@ -14981,11 +14981,11 @@
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="J200">
-        <v>1150</v>
+        <v>296</v>
       </c>
       <c r="K200" t="inlineStr">
         <is>
@@ -15056,11 +15056,11 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J201">
-        <v>296</v>
+        <v>645</v>
       </c>
       <c r="K201" t="inlineStr">
         <is>
@@ -15131,11 +15131,11 @@
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J202">
-        <v>645</v>
+        <v>668</v>
       </c>
       <c r="K202" t="inlineStr">
         <is>
@@ -15191,40 +15191,40 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergade 10</t>
+          <t xml:space="preserve">Skovvej 36</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t xml:space="preserve">6622</t>
+          <t xml:space="preserve">6600</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t xml:space="preserve">9197501</t>
+          <t xml:space="preserve">9691651</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J203">
-        <v>668</v>
+        <v>265</v>
       </c>
       <c r="K203" t="inlineStr">
         <is>
-          <t xml:space="preserve">311290487</t>
+          <t xml:space="preserve">311305978</t>
         </is>
       </c>
       <c r="L203" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
         </is>
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-23</t>
+          <t xml:space="preserve">2028-03-30</t>
         </is>
       </c>
       <c r="N203" t="inlineStr">
@@ -15281,15 +15281,15 @@
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J204">
-        <v>265</v>
+        <v>293</v>
       </c>
       <c r="K204" t="inlineStr">
         <is>
-          <t xml:space="preserve">311305978</t>
+          <t xml:space="preserve">311307544</t>
         </is>
       </c>
       <c r="L204" t="inlineStr">
@@ -15299,7 +15299,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-03-30</t>
+          <t xml:space="preserve">2028-04-10</t>
         </is>
       </c>
       <c r="N204" t="inlineStr">
@@ -15356,11 +15356,11 @@
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J205">
-        <v>293</v>
+        <v>588</v>
       </c>
       <c r="K205" t="inlineStr">
         <is>
@@ -15416,30 +15416,30 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovvej 36</t>
+          <t xml:space="preserve">Blomsterengen 43</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t xml:space="preserve">6600</t>
+          <t xml:space="preserve">6670</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t xml:space="preserve">9691651</t>
+          <t xml:space="preserve">9196503</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J206">
-        <v>588</v>
+        <v>271</v>
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t xml:space="preserve">311307544</t>
+          <t xml:space="preserve">311308332</t>
         </is>
       </c>
       <c r="L206" t="inlineStr">
@@ -15449,7 +15449,7 @@
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-04-10</t>
+          <t xml:space="preserve">2028-04-13</t>
         </is>
       </c>
       <c r="N206" t="inlineStr">
@@ -15491,17 +15491,17 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t xml:space="preserve">Blomsterengen 43</t>
+          <t xml:space="preserve">Skolegade 10</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t xml:space="preserve">6670</t>
+          <t xml:space="preserve">6650</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t xml:space="preserve">9196503</t>
+          <t xml:space="preserve">5032097</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -15510,11 +15510,11 @@
         </is>
       </c>
       <c r="J207">
-        <v>271</v>
+        <v>351</v>
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t xml:space="preserve">311308332</t>
+          <t xml:space="preserve">311309220</t>
         </is>
       </c>
       <c r="L207" t="inlineStr">
@@ -15524,7 +15524,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-04-13</t>
+          <t xml:space="preserve">2028-04-18</t>
         </is>
       </c>
       <c r="N207" t="inlineStr">
@@ -15566,7 +15566,7 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 10</t>
+          <t xml:space="preserve">Skolegade 7</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
@@ -15576,7 +15576,7 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t xml:space="preserve">5032097</t>
+          <t xml:space="preserve">9928625</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -15585,11 +15585,11 @@
         </is>
       </c>
       <c r="J208">
-        <v>351</v>
+        <v>825</v>
       </c>
       <c r="K208" t="inlineStr">
         <is>
-          <t xml:space="preserve">311309220</t>
+          <t xml:space="preserve">311309818</t>
         </is>
       </c>
       <c r="L208" t="inlineStr">
@@ -15599,7 +15599,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-04-18</t>
+          <t xml:space="preserve">2028-04-23</t>
         </is>
       </c>
       <c r="N208" t="inlineStr">
@@ -15641,40 +15641,40 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 7</t>
+          <t xml:space="preserve">Rådhuspassagen 3</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t xml:space="preserve">6650</t>
+          <t xml:space="preserve">6600</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t xml:space="preserve">9928625</t>
+          <t xml:space="preserve">5041004</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J209">
-        <v>825</v>
+        <v>4946</v>
       </c>
       <c r="K209" t="inlineStr">
         <is>
-          <t xml:space="preserve">311309818</t>
+          <t xml:space="preserve">311395853</t>
         </is>
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+          <t xml:space="preserve">EWII Energi A/S</t>
         </is>
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-04-23</t>
+          <t xml:space="preserve">2029-08-30</t>
         </is>
       </c>
       <c r="N209" t="inlineStr">
@@ -15716,7 +15716,7 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rådhuspassagen 3</t>
+          <t xml:space="preserve">Vestergade 2</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
@@ -15726,30 +15726,30 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t xml:space="preserve">5041004</t>
+          <t xml:space="preserve">434528, 434529, 434530, 434531, 434532, 434533, 434878, 434885, 434534, 434535, 434536, 434537, 434870, 434872, 434873, 434874, 434875, 434876, 434877, 434879, 434880, 434881, 434882, 434883, 434884, 434886, 434887, 434888, 434889, 434890, 434891</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J210">
-        <v>4946</v>
+        <v>6338</v>
       </c>
       <c r="K210" t="inlineStr">
         <is>
-          <t xml:space="preserve">311395853</t>
+          <t xml:space="preserve">311402991</t>
         </is>
       </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t xml:space="preserve">EWII Energi A/S</t>
+          <t xml:space="preserve">KEEN MILJØ &amp; ENERGIRÅDGIVNING ApS</t>
         </is>
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-08-30</t>
+          <t xml:space="preserve">2029-10-09</t>
         </is>
       </c>
       <c r="N210" t="inlineStr">
@@ -15791,7 +15791,7 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergade 2</t>
+          <t xml:space="preserve">Lindegade 10</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
@@ -15801,7 +15801,7 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t xml:space="preserve">434528, 434529, 434530, 434531, 434532, 434533, 434878, 434885, 434534, 434535, 434536, 434537, 434870, 434872, 434873, 434874, 434875, 434876, 434877, 434879, 434880, 434881, 434882, 434883, 434884, 434886, 434887, 434888, 434889, 434890, 434891</t>
+          <t xml:space="preserve">5040356</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -15810,11 +15810,11 @@
         </is>
       </c>
       <c r="J211">
-        <v>6338</v>
+        <v>673</v>
       </c>
       <c r="K211" t="inlineStr">
         <is>
-          <t xml:space="preserve">311402991</t>
+          <t xml:space="preserve">311450533</t>
         </is>
       </c>
       <c r="L211" t="inlineStr">
@@ -15824,7 +15824,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-10-09</t>
+          <t xml:space="preserve">2030-07-20</t>
         </is>
       </c>
       <c r="N211" t="inlineStr">
@@ -15866,17 +15866,17 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lindegade 10</t>
+          <t xml:space="preserve">Højmarksvej 20</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t xml:space="preserve">6600</t>
+          <t xml:space="preserve">6670</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t xml:space="preserve">5040356</t>
+          <t xml:space="preserve">5036534</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -15885,21 +15885,21 @@
         </is>
       </c>
       <c r="J212">
-        <v>673</v>
+        <v>1800</v>
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t xml:space="preserve">311450533</t>
+          <t xml:space="preserve">311529161</t>
         </is>
       </c>
       <c r="L212" t="inlineStr">
         <is>
-          <t xml:space="preserve">KEEN MILJØ &amp; ENERGIRÅDGIVNING ApS</t>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
         </is>
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-07-20</t>
+          <t xml:space="preserve">2031-06-18</t>
         </is>
       </c>
       <c r="N212" t="inlineStr">
@@ -15941,17 +15941,17 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t xml:space="preserve">Højmarksvej 20</t>
+          <t xml:space="preserve">Kirkepladsen 1</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t xml:space="preserve">6670</t>
+          <t xml:space="preserve">6660</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t xml:space="preserve">5036534</t>
+          <t xml:space="preserve">5196229</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -15960,11 +15960,11 @@
         </is>
       </c>
       <c r="J213">
-        <v>1800</v>
+        <v>1950</v>
       </c>
       <c r="K213" t="inlineStr">
         <is>
-          <t xml:space="preserve">311529161</t>
+          <t xml:space="preserve">311529164</t>
         </is>
       </c>
       <c r="L213" t="inlineStr">
@@ -16016,17 +16016,17 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkepladsen 1</t>
+          <t xml:space="preserve">Krygersvej 2</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t xml:space="preserve">6660</t>
+          <t xml:space="preserve">6630</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t xml:space="preserve">5196229</t>
+          <t xml:space="preserve">8309304</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -16035,11 +16035,11 @@
         </is>
       </c>
       <c r="J214">
-        <v>1950</v>
+        <v>4954</v>
       </c>
       <c r="K214" t="inlineStr">
         <is>
-          <t xml:space="preserve">311529164</t>
+          <t xml:space="preserve">311529162</t>
         </is>
       </c>
       <c r="L214" t="inlineStr">
@@ -16091,17 +16091,17 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t xml:space="preserve">Krygersvej 2</t>
+          <t xml:space="preserve">Stadionvej 15</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t xml:space="preserve">6630</t>
+          <t xml:space="preserve">6650</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t xml:space="preserve">8309304</t>
+          <t xml:space="preserve">1484897</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -16110,11 +16110,11 @@
         </is>
       </c>
       <c r="J215">
-        <v>4954</v>
+        <v>2189</v>
       </c>
       <c r="K215" t="inlineStr">
         <is>
-          <t xml:space="preserve">311529162</t>
+          <t xml:space="preserve">311529163</t>
         </is>
       </c>
       <c r="L215" t="inlineStr">
@@ -16166,17 +16166,17 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionvej 15</t>
+          <t xml:space="preserve">Skodborg Nørregade 6</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t xml:space="preserve">6650</t>
+          <t xml:space="preserve">6630</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t xml:space="preserve">1484897</t>
+          <t xml:space="preserve">308654</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -16185,21 +16185,21 @@
         </is>
       </c>
       <c r="J216">
-        <v>2189</v>
+        <v>963</v>
       </c>
       <c r="K216" t="inlineStr">
         <is>
-          <t xml:space="preserve">311529163</t>
+          <t xml:space="preserve">311533232</t>
         </is>
       </c>
       <c r="L216" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-06-18</t>
+          <t xml:space="preserve">2031-07-02</t>
         </is>
       </c>
       <c r="N216" t="inlineStr">
@@ -16241,7 +16241,7 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skodborg Nørregade 6</t>
+          <t xml:space="preserve">Rødding Engvej 3</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
@@ -16251,7 +16251,7 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t xml:space="preserve">308654</t>
+          <t xml:space="preserve">5197937</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -16260,21 +16260,21 @@
         </is>
       </c>
       <c r="J217">
-        <v>963</v>
+        <v>1070</v>
       </c>
       <c r="K217" t="inlineStr">
         <is>
-          <t xml:space="preserve">311533232</t>
+          <t xml:space="preserve">311534227</t>
         </is>
       </c>
       <c r="L217" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
         </is>
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-07-02</t>
+          <t xml:space="preserve">2031-07-07</t>
         </is>
       </c>
       <c r="N217" t="inlineStr">
@@ -16331,11 +16331,11 @@
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J218">
-        <v>1070</v>
+        <v>326</v>
       </c>
       <c r="K218" t="inlineStr">
         <is>
@@ -16391,40 +16391,40 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rødding Engvej 3</t>
+          <t xml:space="preserve">Industrivej Vest 18</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t xml:space="preserve">6630</t>
+          <t xml:space="preserve">6600</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t xml:space="preserve">5197937</t>
+          <t xml:space="preserve">10156994</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J219">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="K219" t="inlineStr">
         <is>
-          <t xml:space="preserve">311534227</t>
+          <t xml:space="preserve">311535979</t>
         </is>
       </c>
       <c r="L219" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+          <t xml:space="preserve">Ankersen ApS</t>
         </is>
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-07-07</t>
+          <t xml:space="preserve">2031-07-14</t>
         </is>
       </c>
       <c r="N219" t="inlineStr">
@@ -16466,17 +16466,17 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t xml:space="preserve">Industrivej Vest 18</t>
+          <t xml:space="preserve">Hovborgvej 1</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t xml:space="preserve">6600</t>
+          <t xml:space="preserve">6650</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t xml:space="preserve">10156994</t>
+          <t xml:space="preserve">5037992</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -16485,21 +16485,21 @@
         </is>
       </c>
       <c r="J220">
-        <v>325</v>
+        <v>134</v>
       </c>
       <c r="K220" t="inlineStr">
         <is>
-          <t xml:space="preserve">311535979</t>
+          <t xml:space="preserve">311540206</t>
         </is>
       </c>
       <c r="L220" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ankersen ApS</t>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
         </is>
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-07-14</t>
+          <t xml:space="preserve">2031-08-11</t>
         </is>
       </c>
       <c r="N220" t="inlineStr">
@@ -16556,11 +16556,11 @@
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J221">
-        <v>134</v>
+        <v>294</v>
       </c>
       <c r="K221" t="inlineStr">
         <is>
@@ -16631,11 +16631,11 @@
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J222">
-        <v>294</v>
+        <v>1558</v>
       </c>
       <c r="K222" t="inlineStr">
         <is>
@@ -16706,11 +16706,11 @@
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J223">
-        <v>1558</v>
+        <v>348</v>
       </c>
       <c r="K223" t="inlineStr">
         <is>
@@ -16766,7 +16766,7 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovborgvej 1</t>
+          <t xml:space="preserve">Skolegade 2</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
@@ -16776,20 +16776,20 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t xml:space="preserve">5037992</t>
+          <t xml:space="preserve">5032058</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J224">
-        <v>348</v>
+        <v>2285</v>
       </c>
       <c r="K224" t="inlineStr">
         <is>
-          <t xml:space="preserve">311540206</t>
+          <t xml:space="preserve">311541332</t>
         </is>
       </c>
       <c r="L224" t="inlineStr">
@@ -16799,7 +16799,7 @@
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-11</t>
+          <t xml:space="preserve">2031-08-17</t>
         </is>
       </c>
       <c r="N224" t="inlineStr">
@@ -16856,11 +16856,11 @@
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J225">
-        <v>2285</v>
+        <v>285</v>
       </c>
       <c r="K225" t="inlineStr">
         <is>
@@ -16931,11 +16931,11 @@
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J226">
-        <v>285</v>
+        <v>649</v>
       </c>
       <c r="K226" t="inlineStr">
         <is>
@@ -17006,11 +17006,11 @@
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J227">
-        <v>649</v>
+        <v>1337</v>
       </c>
       <c r="K227" t="inlineStr">
         <is>
@@ -17081,11 +17081,11 @@
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J228">
-        <v>1337</v>
+        <v>461</v>
       </c>
       <c r="K228" t="inlineStr">
         <is>
@@ -17156,11 +17156,11 @@
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J229">
-        <v>461</v>
+        <v>396</v>
       </c>
       <c r="K229" t="inlineStr">
         <is>
@@ -17216,30 +17216,30 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 2</t>
+          <t xml:space="preserve">Østergade 28</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t xml:space="preserve">6650</t>
+          <t xml:space="preserve">6630</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t xml:space="preserve">5032058</t>
+          <t xml:space="preserve">5198538</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J230">
-        <v>396</v>
+        <v>2208</v>
       </c>
       <c r="K230" t="inlineStr">
         <is>
-          <t xml:space="preserve">311541332</t>
+          <t xml:space="preserve">311543399</t>
         </is>
       </c>
       <c r="L230" t="inlineStr">
@@ -17249,7 +17249,7 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-17</t>
+          <t xml:space="preserve">2031-08-26</t>
         </is>
       </c>
       <c r="N230" t="inlineStr">
@@ -17291,7 +17291,7 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østergade 28</t>
+          <t xml:space="preserve">Rytterdam 1C</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
@@ -17301,7 +17301,7 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t xml:space="preserve">5198538</t>
+          <t xml:space="preserve">9252176</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
@@ -17310,11 +17310,11 @@
         </is>
       </c>
       <c r="J231">
-        <v>2208</v>
+        <v>353</v>
       </c>
       <c r="K231" t="inlineStr">
         <is>
-          <t xml:space="preserve">311543399</t>
+          <t xml:space="preserve">311546545</t>
         </is>
       </c>
       <c r="L231" t="inlineStr">
@@ -17324,7 +17324,7 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-26</t>
+          <t xml:space="preserve">2031-09-08</t>
         </is>
       </c>
       <c r="N231" t="inlineStr">
@@ -17366,7 +17366,7 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rytterdam 1C</t>
+          <t xml:space="preserve">Rytterdam 9</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
@@ -17381,11 +17381,11 @@
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J232">
-        <v>353</v>
+        <v>8186</v>
       </c>
       <c r="K232" t="inlineStr">
         <is>
@@ -17456,11 +17456,11 @@
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J233">
-        <v>8186</v>
+        <v>586</v>
       </c>
       <c r="K233" t="inlineStr">
         <is>
@@ -17531,11 +17531,11 @@
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J234">
-        <v>586</v>
+        <v>665</v>
       </c>
       <c r="K234" t="inlineStr">
         <is>
@@ -17591,30 +17591,30 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rytterdam 9</t>
+          <t xml:space="preserve">Åttevej 8</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t xml:space="preserve">6630</t>
+          <t xml:space="preserve">6683</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t xml:space="preserve">9252176</t>
+          <t xml:space="preserve">5034272</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J235">
-        <v>665</v>
+        <v>1625</v>
       </c>
       <c r="K235" t="inlineStr">
         <is>
-          <t xml:space="preserve">311546545</t>
+          <t xml:space="preserve">311547050</t>
         </is>
       </c>
       <c r="L235" t="inlineStr">
@@ -17624,7 +17624,7 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-08</t>
+          <t xml:space="preserve">2031-09-09</t>
         </is>
       </c>
       <c r="N235" t="inlineStr">
@@ -17681,15 +17681,15 @@
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J236">
-        <v>1625</v>
+        <v>339</v>
       </c>
       <c r="K236" t="inlineStr">
         <is>
-          <t xml:space="preserve">311547050</t>
+          <t xml:space="preserve">311547065</t>
         </is>
       </c>
       <c r="L236" t="inlineStr">
@@ -17756,11 +17756,11 @@
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J237">
-        <v>339</v>
+        <v>218</v>
       </c>
       <c r="K237" t="inlineStr">
         <is>
@@ -17831,15 +17831,15 @@
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J238">
-        <v>218</v>
+        <v>348</v>
       </c>
       <c r="K238" t="inlineStr">
         <is>
-          <t xml:space="preserve">311547065</t>
+          <t xml:space="preserve">311547018</t>
         </is>
       </c>
       <c r="L238" t="inlineStr">
@@ -17891,30 +17891,30 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t xml:space="preserve">Åttevej 8</t>
+          <t xml:space="preserve">Parkvej 4</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t xml:space="preserve">6683</t>
+          <t xml:space="preserve">6630</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t xml:space="preserve">5034272</t>
+          <t xml:space="preserve">5198848</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J239">
-        <v>348</v>
+        <v>950</v>
       </c>
       <c r="K239" t="inlineStr">
         <is>
-          <t xml:space="preserve">311547018</t>
+          <t xml:space="preserve">311572718</t>
         </is>
       </c>
       <c r="L239" t="inlineStr">
@@ -17924,7 +17924,7 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-09</t>
+          <t xml:space="preserve">2031-09-24</t>
         </is>
       </c>
       <c r="N239" t="inlineStr">
@@ -17966,17 +17966,17 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parkvej 4</t>
+          <t xml:space="preserve">Højmarksvej 16</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t xml:space="preserve">6630</t>
+          <t xml:space="preserve">6670</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t xml:space="preserve">5198848</t>
+          <t xml:space="preserve">5036460</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
@@ -17985,11 +17985,11 @@
         </is>
       </c>
       <c r="J240">
-        <v>950</v>
+        <v>1255</v>
       </c>
       <c r="K240" t="inlineStr">
         <is>
-          <t xml:space="preserve">311572718</t>
+          <t xml:space="preserve">311560309</t>
         </is>
       </c>
       <c r="L240" t="inlineStr">
@@ -17999,7 +17999,7 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-24</t>
+          <t xml:space="preserve">2031-11-08</t>
         </is>
       </c>
       <c r="N240" t="inlineStr">
@@ -18056,11 +18056,11 @@
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J241">
-        <v>1255</v>
+        <v>1422</v>
       </c>
       <c r="K241" t="inlineStr">
         <is>
@@ -18131,11 +18131,11 @@
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">20</t>
         </is>
       </c>
       <c r="J242">
-        <v>1422</v>
+        <v>962</v>
       </c>
       <c r="K242" t="inlineStr">
         <is>
@@ -18206,11 +18206,11 @@
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J243">
-        <v>962</v>
+        <v>1499</v>
       </c>
       <c r="K243" t="inlineStr">
         <is>
@@ -18281,11 +18281,11 @@
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J244">
-        <v>1499</v>
+        <v>1232</v>
       </c>
       <c r="K244" t="inlineStr">
         <is>
@@ -18356,11 +18356,11 @@
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J245">
-        <v>1232</v>
+        <v>838</v>
       </c>
       <c r="K245" t="inlineStr">
         <is>
@@ -18431,11 +18431,11 @@
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J246">
-        <v>838</v>
+        <v>587</v>
       </c>
       <c r="K246" t="inlineStr">
         <is>
@@ -18506,11 +18506,11 @@
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J247">
-        <v>587</v>
+        <v>412</v>
       </c>
       <c r="K247" t="inlineStr">
         <is>
@@ -18566,30 +18566,30 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t xml:space="preserve">Højmarksvej 16</t>
+          <t xml:space="preserve">Nørretoft 2</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t xml:space="preserve">6670</t>
+          <t xml:space="preserve">6660</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t xml:space="preserve">5036460</t>
+          <t xml:space="preserve">5196345</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J248">
-        <v>412</v>
+        <v>226</v>
       </c>
       <c r="K248" t="inlineStr">
         <is>
-          <t xml:space="preserve">311560309</t>
+          <t xml:space="preserve">311560551</t>
         </is>
       </c>
       <c r="L248" t="inlineStr">
@@ -18599,7 +18599,7 @@
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-08</t>
+          <t xml:space="preserve">2031-11-09</t>
         </is>
       </c>
       <c r="N248" t="inlineStr">
@@ -18656,11 +18656,11 @@
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J249">
-        <v>226</v>
+        <v>213</v>
       </c>
       <c r="K249" t="inlineStr">
         <is>
@@ -18716,40 +18716,40 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørretoft 2</t>
+          <t xml:space="preserve">Knudevejen 17A</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t xml:space="preserve">6660</t>
+          <t xml:space="preserve">6600</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t xml:space="preserve">5196345</t>
+          <t xml:space="preserve">7813581</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J250">
-        <v>213</v>
+        <v>386</v>
       </c>
       <c r="K250" t="inlineStr">
         <is>
-          <t xml:space="preserve">311560551</t>
+          <t xml:space="preserve">311660921</t>
         </is>
       </c>
       <c r="L250" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+          <t xml:space="preserve">Murbyg ApS</t>
         </is>
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-09</t>
+          <t xml:space="preserve">2033-02-17</t>
         </is>
       </c>
       <c r="N250" t="inlineStr">
@@ -18791,7 +18791,7 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t xml:space="preserve">Knudevejen 17A</t>
+          <t xml:space="preserve">Knudevejen 17B</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
@@ -18806,7 +18806,7 @@
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J251">
@@ -18881,11 +18881,11 @@
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">50</t>
         </is>
       </c>
       <c r="J252">
-        <v>386</v>
+        <v>103</v>
       </c>
       <c r="K252" t="inlineStr">
         <is>
@@ -18956,11 +18956,11 @@
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t xml:space="preserve">50</t>
+          <t xml:space="preserve">61</t>
         </is>
       </c>
       <c r="J253">
-        <v>103</v>
+        <v>130</v>
       </c>
       <c r="K253" t="inlineStr">
         <is>
@@ -19031,11 +19031,11 @@
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t xml:space="preserve">61</t>
+          <t xml:space="preserve">69</t>
         </is>
       </c>
       <c r="J254">
-        <v>130</v>
+        <v>328</v>
       </c>
       <c r="K254" t="inlineStr">
         <is>
@@ -19091,40 +19091,40 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t xml:space="preserve">Knudevejen 17B</t>
+          <t xml:space="preserve">Borgergade 110</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t xml:space="preserve">6600</t>
+          <t xml:space="preserve">6752</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t xml:space="preserve">7813581</t>
+          <t xml:space="preserve">310746</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t xml:space="preserve">69</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J255">
-        <v>328</v>
+        <v>912</v>
       </c>
       <c r="K255" t="inlineStr">
         <is>
-          <t xml:space="preserve">311660921</t>
+          <t xml:space="preserve">311730609</t>
         </is>
       </c>
       <c r="L255" t="inlineStr">
         <is>
-          <t xml:space="preserve">Murbyg ApS</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-02-17</t>
+          <t xml:space="preserve">2033-12-20</t>
         </is>
       </c>
       <c r="N255" t="inlineStr">
@@ -19166,30 +19166,30 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t xml:space="preserve">Borgergade 110</t>
+          <t xml:space="preserve">Drejervej 7</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t xml:space="preserve">6752</t>
+          <t xml:space="preserve">6600</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t xml:space="preserve">310746</t>
+          <t xml:space="preserve">5043606</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J256">
-        <v>912</v>
+        <v>2188</v>
       </c>
       <c r="K256" t="inlineStr">
         <is>
-          <t xml:space="preserve">311730609</t>
+          <t xml:space="preserve">311740342</t>
         </is>
       </c>
       <c r="L256" t="inlineStr">
@@ -19199,7 +19199,7 @@
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-20</t>
+          <t xml:space="preserve">2034-02-21</t>
         </is>
       </c>
       <c r="N256" t="inlineStr">
@@ -19241,7 +19241,7 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t xml:space="preserve">Drejervej 7</t>
+          <t xml:space="preserve">Drejervej 9</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
@@ -19256,11 +19256,11 @@
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J257">
-        <v>2188</v>
+        <v>182</v>
       </c>
       <c r="K257" t="inlineStr">
         <is>
@@ -19316,7 +19316,7 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t xml:space="preserve">Drejervej 9</t>
+          <t xml:space="preserve">Rugholmvej 16</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
@@ -19326,30 +19326,30 @@
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t xml:space="preserve">5043606</t>
+          <t xml:space="preserve">100002769</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J258">
-        <v>182</v>
+        <v>294</v>
       </c>
       <c r="K258" t="inlineStr">
         <is>
-          <t xml:space="preserve">311740342</t>
+          <t xml:space="preserve">311791576</t>
         </is>
       </c>
       <c r="L258" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-02-21</t>
+          <t xml:space="preserve">2034-10-15</t>
         </is>
       </c>
       <c r="N258" t="inlineStr">
@@ -19406,11 +19406,11 @@
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J259">
-        <v>294</v>
+        <v>158</v>
       </c>
       <c r="K259" t="inlineStr">
         <is>
@@ -19466,40 +19466,40 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rugholmvej 16</t>
+          <t xml:space="preserve">Vestergade 19</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t xml:space="preserve">6600</t>
+          <t xml:space="preserve">6670</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t xml:space="preserve">100002769</t>
+          <t xml:space="preserve">5035619</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J260">
-        <v>158</v>
+        <v>315</v>
       </c>
       <c r="K260" t="inlineStr">
         <is>
-          <t xml:space="preserve">311791576</t>
+          <t xml:space="preserve">311814507</t>
         </is>
       </c>
       <c r="L260" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">OBH</t>
         </is>
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-10-15</t>
+          <t xml:space="preserve">2035-02-28</t>
         </is>
       </c>
       <c r="N260" t="inlineStr">
@@ -19541,7 +19541,7 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergade 19</t>
+          <t xml:space="preserve">Højmarksvej 18</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
@@ -19551,7 +19551,7 @@
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t xml:space="preserve">5035619</t>
+          <t xml:space="preserve">5036533</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
@@ -19560,21 +19560,21 @@
         </is>
       </c>
       <c r="J261">
-        <v>315</v>
+        <v>2243</v>
       </c>
       <c r="K261" t="inlineStr">
         <is>
-          <t xml:space="preserve">311814507</t>
+          <t xml:space="preserve">311894920</t>
         </is>
       </c>
       <c r="L261" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-02-28</t>
+          <t xml:space="preserve">2036-04-17</t>
         </is>
       </c>
       <c r="N261" t="inlineStr">
@@ -19631,15 +19631,15 @@
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J262">
-        <v>2243</v>
+        <v>3900</v>
       </c>
       <c r="K262" t="inlineStr">
         <is>
-          <t xml:space="preserve">311894920</t>
+          <t xml:space="preserve">311894909</t>
         </is>
       </c>
       <c r="L262" t="inlineStr">
@@ -19691,17 +19691,17 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t xml:space="preserve">Højmarksvej 18</t>
+          <t xml:space="preserve">Møllevænget 5</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t xml:space="preserve">6670</t>
+          <t xml:space="preserve">6622</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t xml:space="preserve">5036533</t>
+          <t xml:space="preserve">737305, 5019907</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
@@ -19710,11 +19710,11 @@
         </is>
       </c>
       <c r="J263">
-        <v>3900</v>
+        <v>2050</v>
       </c>
       <c r="K263" t="inlineStr">
         <is>
-          <t xml:space="preserve">311894909</t>
+          <t xml:space="preserve">311894926</t>
         </is>
       </c>
       <c r="L263" t="inlineStr">
@@ -19766,30 +19766,30 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møllevænget 5</t>
+          <t xml:space="preserve">Ørstedvej 10</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t xml:space="preserve">6622</t>
+          <t xml:space="preserve">6630</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t xml:space="preserve">737305, 5019907</t>
+          <t xml:space="preserve">737335, 5186260</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J264">
-        <v>2050</v>
+        <v>537</v>
       </c>
       <c r="K264" t="inlineStr">
         <is>
-          <t xml:space="preserve">311894926</t>
+          <t xml:space="preserve">311894879</t>
         </is>
       </c>
       <c r="L264" t="inlineStr">
@@ -19841,30 +19841,30 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ørstedvej 10</t>
+          <t xml:space="preserve">Stadionvej 2A</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t xml:space="preserve">6630</t>
+          <t xml:space="preserve">6752</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t xml:space="preserve">737335, 5186260</t>
+          <t xml:space="preserve">737383, 5045451</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J265">
-        <v>537</v>
+        <v>423</v>
       </c>
       <c r="K265" t="inlineStr">
         <is>
-          <t xml:space="preserve">311894879</t>
+          <t xml:space="preserve">311895815</t>
         </is>
       </c>
       <c r="L265" t="inlineStr">
@@ -19874,7 +19874,7 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-17</t>
+          <t xml:space="preserve">2036-04-22</t>
         </is>
       </c>
       <c r="N265" t="inlineStr">
@@ -19931,15 +19931,15 @@
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J266">
-        <v>423</v>
+        <v>1665</v>
       </c>
       <c r="K266" t="inlineStr">
         <is>
-          <t xml:space="preserve">311895815</t>
+          <t xml:space="preserve">311896169</t>
         </is>
       </c>
       <c r="L266" t="inlineStr">
@@ -19949,7 +19949,7 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-22</t>
+          <t xml:space="preserve">2036-04-23</t>
         </is>
       </c>
       <c r="N266" t="inlineStr">
@@ -20006,15 +20006,15 @@
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J267">
-        <v>1665</v>
+        <v>273</v>
       </c>
       <c r="K267" t="inlineStr">
         <is>
-          <t xml:space="preserve">311896169</t>
+          <t xml:space="preserve">311896606</t>
         </is>
       </c>
       <c r="L267" t="inlineStr">
@@ -20024,7 +20024,7 @@
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-23</t>
+          <t xml:space="preserve">2036-04-24</t>
         </is>
       </c>
       <c r="N267" t="inlineStr">
@@ -20066,30 +20066,30 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionvej 2A</t>
+          <t xml:space="preserve">Bækkevej 30</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t xml:space="preserve">6752</t>
+          <t xml:space="preserve">6650</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t xml:space="preserve">737383, 5045451</t>
+          <t xml:space="preserve">737370, 5037333</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J268">
-        <v>273</v>
+        <v>953</v>
       </c>
       <c r="K268" t="inlineStr">
         <is>
-          <t xml:space="preserve">311896606</t>
+          <t xml:space="preserve">311905030</t>
         </is>
       </c>
       <c r="L268" t="inlineStr">
@@ -20099,7 +20099,7 @@
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-24</t>
+          <t xml:space="preserve">2036-06-01</t>
         </is>
       </c>
       <c r="N268" t="inlineStr">
@@ -20141,17 +20141,17 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bækkevej 30</t>
+          <t xml:space="preserve">Bækkevej 9A</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t xml:space="preserve">6650</t>
+          <t xml:space="preserve">6621</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t xml:space="preserve">737370, 5037333</t>
+          <t xml:space="preserve">5020950</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
@@ -20160,11 +20160,11 @@
         </is>
       </c>
       <c r="J269">
-        <v>953</v>
+        <v>1868</v>
       </c>
       <c r="K269" t="inlineStr">
         <is>
-          <t xml:space="preserve">311905030</t>
+          <t xml:space="preserve">311905028</t>
         </is>
       </c>
       <c r="L269" t="inlineStr">
@@ -20216,30 +20216,30 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bækkevej 9A</t>
+          <t xml:space="preserve">Lindevej 7A</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t xml:space="preserve">6621</t>
+          <t xml:space="preserve">6682</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t xml:space="preserve">5020950</t>
+          <t xml:space="preserve">737412, 5037833</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">104</t>
         </is>
       </c>
       <c r="J270">
-        <v>1868</v>
+        <v>1348</v>
       </c>
       <c r="K270" t="inlineStr">
         <is>
-          <t xml:space="preserve">311905028</t>
+          <t xml:space="preserve">311914611</t>
         </is>
       </c>
       <c r="L270" t="inlineStr">
@@ -20291,7 +20291,7 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lindevej 7A</t>
+          <t xml:space="preserve">Lindevej 7C</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
@@ -20301,20 +20301,20 @@
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t xml:space="preserve">737412, 5037833</t>
+          <t xml:space="preserve">5037833</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t xml:space="preserve">104</t>
+          <t xml:space="preserve">101</t>
         </is>
       </c>
       <c r="J271">
-        <v>1348</v>
+        <v>96</v>
       </c>
       <c r="K271" t="inlineStr">
         <is>
-          <t xml:space="preserve">311914611</t>
+          <t xml:space="preserve">311905034</t>
         </is>
       </c>
       <c r="L271" t="inlineStr">
@@ -20366,30 +20366,30 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lindevej 7C</t>
+          <t xml:space="preserve">Holleskovvej 4</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t xml:space="preserve">6682</t>
+          <t xml:space="preserve">6683</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t xml:space="preserve">5037833</t>
+          <t xml:space="preserve">737386, 5034767</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t xml:space="preserve">101</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J272">
-        <v>96</v>
+        <v>452</v>
       </c>
       <c r="K272" t="inlineStr">
         <is>
-          <t xml:space="preserve">311905034</t>
+          <t xml:space="preserve">311905606</t>
         </is>
       </c>
       <c r="L272" t="inlineStr">
@@ -20399,7 +20399,7 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-06-01</t>
+          <t xml:space="preserve">2036-06-04</t>
         </is>
       </c>
       <c r="N272" t="inlineStr">
@@ -20441,17 +20441,17 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holleskovvej 4</t>
+          <t xml:space="preserve">Skolegade 1</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t xml:space="preserve">6683</t>
+          <t xml:space="preserve">6630</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t xml:space="preserve">737386, 5034767</t>
+          <t xml:space="preserve">5195366</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
@@ -20460,11 +20460,11 @@
         </is>
       </c>
       <c r="J273">
-        <v>452</v>
+        <v>1052</v>
       </c>
       <c r="K273" t="inlineStr">
         <is>
-          <t xml:space="preserve">311905606</t>
+          <t xml:space="preserve">311905369</t>
         </is>
       </c>
       <c r="L273" t="inlineStr">
@@ -20516,7 +20516,7 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 1</t>
+          <t xml:space="preserve">Søndergyden 17</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
@@ -20526,7 +20526,7 @@
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t xml:space="preserve">5195366</t>
+          <t xml:space="preserve">9196089</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
@@ -20535,11 +20535,11 @@
         </is>
       </c>
       <c r="J274">
-        <v>1052</v>
+        <v>1782</v>
       </c>
       <c r="K274" t="inlineStr">
         <is>
-          <t xml:space="preserve">311905369</t>
+          <t xml:space="preserve">311905611</t>
         </is>
       </c>
       <c r="L274" t="inlineStr">
@@ -20591,30 +20591,30 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndergyden 17</t>
+          <t xml:space="preserve">Byagervej 3</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t xml:space="preserve">6630</t>
+          <t xml:space="preserve">6650</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t xml:space="preserve">9196089</t>
+          <t xml:space="preserve">737365, 5032515</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J275">
-        <v>1782</v>
+        <v>2937</v>
       </c>
       <c r="K275" t="inlineStr">
         <is>
-          <t xml:space="preserve">311905611</t>
+          <t xml:space="preserve">311907452</t>
         </is>
       </c>
       <c r="L275" t="inlineStr">
@@ -20624,7 +20624,7 @@
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-06-04</t>
+          <t xml:space="preserve">2036-06-11</t>
         </is>
       </c>
       <c r="N275" t="inlineStr">
@@ -20666,30 +20666,30 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t xml:space="preserve">Byagervej 3</t>
+          <t xml:space="preserve">Petersmindevej 1</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t xml:space="preserve">6650</t>
+          <t xml:space="preserve">6600</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t xml:space="preserve">737365, 5032515</t>
+          <t xml:space="preserve">7955800</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J276">
-        <v>2937</v>
+        <v>6676</v>
       </c>
       <c r="K276" t="inlineStr">
         <is>
-          <t xml:space="preserve">311907452</t>
+          <t xml:space="preserve">311915214</t>
         </is>
       </c>
       <c r="L276" t="inlineStr">
@@ -20699,7 +20699,7 @@
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-06-11</t>
+          <t xml:space="preserve">2036-07-20</t>
         </is>
       </c>
       <c r="N276" t="inlineStr">
@@ -20756,15 +20756,15 @@
       </c>
       <c r="I277" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J277">
-        <v>6676</v>
+        <v>2183</v>
       </c>
       <c r="K277" t="inlineStr">
         <is>
-          <t xml:space="preserve">311915214</t>
+          <t xml:space="preserve">311915210</t>
         </is>
       </c>
       <c r="L277" t="inlineStr">
@@ -20831,15 +20831,15 @@
       </c>
       <c r="I278" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J278">
-        <v>2183</v>
+        <v>310</v>
       </c>
       <c r="K278" t="inlineStr">
         <is>
-          <t xml:space="preserve">311915210</t>
+          <t xml:space="preserve">311915206</t>
         </is>
       </c>
       <c r="L278" t="inlineStr">
@@ -20906,15 +20906,15 @@
       </c>
       <c r="I279" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J279">
-        <v>310</v>
+        <v>907</v>
       </c>
       <c r="K279" t="inlineStr">
         <is>
-          <t xml:space="preserve">311915206</t>
+          <t xml:space="preserve">311915205</t>
         </is>
       </c>
       <c r="L279" t="inlineStr">
@@ -20981,15 +20981,15 @@
       </c>
       <c r="I280" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J280">
-        <v>907</v>
+        <v>1135</v>
       </c>
       <c r="K280" t="inlineStr">
         <is>
-          <t xml:space="preserve">311915205</t>
+          <t xml:space="preserve">311915208</t>
         </is>
       </c>
       <c r="L280" t="inlineStr">
@@ -21056,15 +21056,15 @@
       </c>
       <c r="I281" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J281">
-        <v>1135</v>
+        <v>1397</v>
       </c>
       <c r="K281" t="inlineStr">
         <is>
-          <t xml:space="preserve">311915208</t>
+          <t xml:space="preserve">311915207</t>
         </is>
       </c>
       <c r="L281" t="inlineStr">
@@ -21116,30 +21116,30 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t xml:space="preserve">Petersmindevej 1</t>
+          <t xml:space="preserve">Ørstedvej 10</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t xml:space="preserve">6600</t>
+          <t xml:space="preserve">6630</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t xml:space="preserve">7955800</t>
+          <t xml:space="preserve">737335, 5186260</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J282">
-        <v>1397</v>
+        <v>244</v>
       </c>
       <c r="K282" t="inlineStr">
         <is>
-          <t xml:space="preserve">311915207</t>
+          <t xml:space="preserve">311916957</t>
         </is>
       </c>
       <c r="L282" t="inlineStr">
@@ -21149,7 +21149,7 @@
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-07-20</t>
+          <t xml:space="preserve">2036-08-03</t>
         </is>
       </c>
       <c r="N282" t="inlineStr">
@@ -21191,40 +21191,40 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ørstedvej 10</t>
+          <t xml:space="preserve">Petersmindevej 2A</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t xml:space="preserve">6630</t>
+          <t xml:space="preserve">6600</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t xml:space="preserve">737335, 5186260</t>
+          <t xml:space="preserve">9203884</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">100</t>
         </is>
       </c>
       <c r="J283">
-        <v>244</v>
+        <v>1872</v>
       </c>
       <c r="K283" t="inlineStr">
         <is>
-          <t xml:space="preserve">311916957</t>
+          <t xml:space="preserve">311922670</t>
         </is>
       </c>
       <c r="L283" t="inlineStr">
         <is>
-          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+          <t xml:space="preserve">Norca Aps</t>
         </is>
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-08-03</t>
+          <t xml:space="preserve">2036-08-31</t>
         </is>
       </c>
       <c r="N283" t="inlineStr">
@@ -21266,40 +21266,40 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t xml:space="preserve">Petersmindevej 2A</t>
+          <t xml:space="preserve">Lille Veumvej 6</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t xml:space="preserve">6600</t>
+          <t xml:space="preserve">6650</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t xml:space="preserve">9203884</t>
+          <t xml:space="preserve">5031183</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t xml:space="preserve">100</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J284">
-        <v>1872</v>
+        <v>1056</v>
       </c>
       <c r="K284" t="inlineStr">
         <is>
-          <t xml:space="preserve">311922670</t>
+          <t xml:space="preserve">311923191</t>
         </is>
       </c>
       <c r="L284" t="inlineStr">
         <is>
-          <t xml:space="preserve">Norca Aps</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-08-31</t>
+          <t xml:space="preserve">2036-09-02</t>
         </is>
       </c>
       <c r="N284" t="inlineStr">
@@ -21341,17 +21341,17 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lille Veumvej 6</t>
+          <t xml:space="preserve">Ø. Skibelundvej 15</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t xml:space="preserve">6650</t>
+          <t xml:space="preserve">6600</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t xml:space="preserve">5031183</t>
+          <t xml:space="preserve">5039005</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
@@ -21360,11 +21360,11 @@
         </is>
       </c>
       <c r="J285">
-        <v>1056</v>
+        <v>326</v>
       </c>
       <c r="K285" t="inlineStr">
         <is>
-          <t xml:space="preserve">311923191</t>
+          <t xml:space="preserve">311923198</t>
         </is>
       </c>
       <c r="L285" t="inlineStr">
@@ -21416,17 +21416,17 @@
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ø. Skibelundvej 15</t>
+          <t xml:space="preserve">Stadionvej 6</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t xml:space="preserve">6600</t>
+          <t xml:space="preserve">6650</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t xml:space="preserve">5039005</t>
+          <t xml:space="preserve">5032443</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
@@ -21435,11 +21435,11 @@
         </is>
       </c>
       <c r="J286">
-        <v>326</v>
+        <v>656</v>
       </c>
       <c r="K286" t="inlineStr">
         <is>
-          <t xml:space="preserve">311923198</t>
+          <t xml:space="preserve">311924085</t>
         </is>
       </c>
       <c r="L286" t="inlineStr">
@@ -21449,7 +21449,7 @@
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-09-02</t>
+          <t xml:space="preserve">2036-09-07</t>
         </is>
       </c>
       <c r="N286" t="inlineStr">
@@ -21491,17 +21491,17 @@
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionvej 6</t>
+          <t xml:space="preserve">Solhøj 2</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t xml:space="preserve">6650</t>
+          <t xml:space="preserve">6600</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t xml:space="preserve">5032443</t>
+          <t xml:space="preserve">5019115</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
@@ -21510,11 +21510,11 @@
         </is>
       </c>
       <c r="J287">
-        <v>656</v>
+        <v>196</v>
       </c>
       <c r="K287" t="inlineStr">
         <is>
-          <t xml:space="preserve">311924085</t>
+          <t xml:space="preserve">311924311</t>
         </is>
       </c>
       <c r="L287" t="inlineStr">
@@ -21524,7 +21524,7 @@
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-09-07</t>
+          <t xml:space="preserve">2036-09-08</t>
         </is>
       </c>
       <c r="N287" t="inlineStr">
@@ -21566,30 +21566,30 @@
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t xml:space="preserve">Solhøj 2</t>
+          <t xml:space="preserve">Byagervej 1</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t xml:space="preserve">6600</t>
+          <t xml:space="preserve">6650</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t xml:space="preserve">5019115</t>
+          <t xml:space="preserve">5032515</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J288">
-        <v>196</v>
+        <v>555</v>
       </c>
       <c r="K288" t="inlineStr">
         <is>
-          <t xml:space="preserve">311924311</t>
+          <t xml:space="preserve">311925241</t>
         </is>
       </c>
       <c r="L288" t="inlineStr">
@@ -21599,7 +21599,7 @@
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-09-08</t>
+          <t xml:space="preserve">2036-09-11</t>
         </is>
       </c>
       <c r="N288" t="inlineStr">
@@ -21641,17 +21641,17 @@
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t xml:space="preserve">Byagervej 1</t>
+          <t xml:space="preserve">Lindevej 5</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t xml:space="preserve">6650</t>
+          <t xml:space="preserve">6682</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t xml:space="preserve">5032515</t>
+          <t xml:space="preserve">5037833</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
@@ -21660,11 +21660,11 @@
         </is>
       </c>
       <c r="J289">
-        <v>555</v>
+        <v>443</v>
       </c>
       <c r="K289" t="inlineStr">
         <is>
-          <t xml:space="preserve">311925241</t>
+          <t xml:space="preserve">311925148</t>
         </is>
       </c>
       <c r="L289" t="inlineStr">
@@ -21731,15 +21731,15 @@
       </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J290">
-        <v>443</v>
+        <v>169</v>
       </c>
       <c r="K290" t="inlineStr">
         <is>
-          <t xml:space="preserve">311925148</t>
+          <t xml:space="preserve">311925146</t>
         </is>
       </c>
       <c r="L290" t="inlineStr">
@@ -21791,7 +21791,7 @@
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lindevej 5</t>
+          <t xml:space="preserve">Lindevej 7B</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
@@ -21806,15 +21806,15 @@
       </c>
       <c r="I291" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">201</t>
         </is>
       </c>
       <c r="J291">
-        <v>169</v>
+        <v>118</v>
       </c>
       <c r="K291" t="inlineStr">
         <is>
-          <t xml:space="preserve">311925146</t>
+          <t xml:space="preserve">311925144</t>
         </is>
       </c>
       <c r="L291" t="inlineStr">
@@ -21866,30 +21866,30 @@
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lindevej 7B</t>
+          <t xml:space="preserve">Dixensvej 1A</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t xml:space="preserve">6682</t>
+          <t xml:space="preserve">6630</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t xml:space="preserve">5037833</t>
+          <t xml:space="preserve">5185767</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
         <is>
-          <t xml:space="preserve">201</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J292">
-        <v>118</v>
+        <v>765</v>
       </c>
       <c r="K292" t="inlineStr">
         <is>
-          <t xml:space="preserve">311925144</t>
+          <t xml:space="preserve">311925437</t>
         </is>
       </c>
       <c r="L292" t="inlineStr">
@@ -21899,7 +21899,7 @@
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-09-11</t>
+          <t xml:space="preserve">2036-09-14</t>
         </is>
       </c>
       <c r="N292" t="inlineStr">
@@ -21941,7 +21941,7 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dixensvej 1A</t>
+          <t xml:space="preserve">Jels Søndergade 17A</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
@@ -21951,7 +21951,7 @@
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t xml:space="preserve">5185767</t>
+          <t xml:space="preserve">5185936</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
@@ -21960,11 +21960,11 @@
         </is>
       </c>
       <c r="J293">
-        <v>765</v>
+        <v>270</v>
       </c>
       <c r="K293" t="inlineStr">
         <is>
-          <t xml:space="preserve">311925437</t>
+          <t xml:space="preserve">311926101</t>
         </is>
       </c>
       <c r="L293" t="inlineStr">
@@ -21974,7 +21974,7 @@
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-09-14</t>
+          <t xml:space="preserve">2036-09-16</t>
         </is>
       </c>
       <c r="N293" t="inlineStr">

--- a/public/exports-from-60/29189838.xlsx
+++ b/public/exports-from-60/29189838.xlsx
@@ -13616,40 +13616,40 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 29</t>
+          <t xml:space="preserve">Højmarksvej 18B</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t xml:space="preserve">6621</t>
+          <t xml:space="preserve">6670</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t xml:space="preserve">5021457</t>
+          <t xml:space="preserve">8894116</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J182">
-        <v>184</v>
+        <v>589</v>
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t xml:space="preserve">311276142</t>
+          <t xml:space="preserve">311285343</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-10-02</t>
+          <t xml:space="preserve">2027-11-23</t>
         </is>
       </c>
       <c r="N182" t="inlineStr">
@@ -13691,17 +13691,17 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadion Alle 2</t>
+          <t xml:space="preserve">Skolegade 1B</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t xml:space="preserve">6621</t>
+          <t xml:space="preserve">6630</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t xml:space="preserve">5021457</t>
+          <t xml:space="preserve">5195702</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -13710,21 +13710,21 @@
         </is>
       </c>
       <c r="J183">
-        <v>1006</v>
+        <v>695</v>
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t xml:space="preserve">311276139</t>
+          <t xml:space="preserve">311286934</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-10-02</t>
+          <t xml:space="preserve">2027-12-03</t>
         </is>
       </c>
       <c r="N183" t="inlineStr">
@@ -13766,40 +13766,40 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadion Alle 2</t>
+          <t xml:space="preserve">Nordre Industrivej 20</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t xml:space="preserve">6621</t>
+          <t xml:space="preserve">6630</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t xml:space="preserve">5021457</t>
+          <t xml:space="preserve">5198440</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J184">
-        <v>1360</v>
+        <v>721</v>
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t xml:space="preserve">311276139</t>
+          <t xml:space="preserve">311287623</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
         </is>
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-10-02</t>
+          <t xml:space="preserve">2027-12-07</t>
         </is>
       </c>
       <c r="N184" t="inlineStr">
@@ -13841,40 +13841,40 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadion Alle 2</t>
+          <t xml:space="preserve">Maltvej 58</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t xml:space="preserve">6621</t>
+          <t xml:space="preserve">6600</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t xml:space="preserve">5021457</t>
+          <t xml:space="preserve">5039208</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J185">
-        <v>536</v>
+        <v>3216</v>
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t xml:space="preserve">311276139</t>
+          <t xml:space="preserve">311288120</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-10-02</t>
+          <t xml:space="preserve">2027-12-11</t>
         </is>
       </c>
       <c r="N185" t="inlineStr">
@@ -13916,17 +13916,17 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t xml:space="preserve">Højmarksvej 18B</t>
+          <t xml:space="preserve">Møllevænget 3</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t xml:space="preserve">6670</t>
+          <t xml:space="preserve">6622</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t xml:space="preserve">8894116</t>
+          <t xml:space="preserve">5019884</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -13935,11 +13935,11 @@
         </is>
       </c>
       <c r="J186">
-        <v>589</v>
+        <v>442</v>
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t xml:space="preserve">311285343</t>
+          <t xml:space="preserve">311288925</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
@@ -13949,7 +13949,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-23</t>
+          <t xml:space="preserve">2027-12-15</t>
         </is>
       </c>
       <c r="N186" t="inlineStr">
@@ -13991,40 +13991,40 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 1B</t>
+          <t xml:space="preserve">Bakkevej 26</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t xml:space="preserve">6630</t>
+          <t xml:space="preserve">6600</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t xml:space="preserve">5195702</t>
+          <t xml:space="preserve">8097595</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J187">
-        <v>695</v>
+        <v>1538</v>
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286934</t>
+          <t xml:space="preserve">311289326</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
         </is>
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-03</t>
+          <t xml:space="preserve">2027-12-18</t>
         </is>
       </c>
       <c r="N187" t="inlineStr">
@@ -14066,30 +14066,30 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nordre Industrivej 20</t>
+          <t xml:space="preserve">Bakkevej 26</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t xml:space="preserve">6630</t>
+          <t xml:space="preserve">6600</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t xml:space="preserve">5198440</t>
+          <t xml:space="preserve">8097595</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J188">
-        <v>721</v>
+        <v>2669</v>
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t xml:space="preserve">311287623</t>
+          <t xml:space="preserve">311289326</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
@@ -14099,7 +14099,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-07</t>
+          <t xml:space="preserve">2027-12-18</t>
         </is>
       </c>
       <c r="N188" t="inlineStr">
@@ -14141,7 +14141,7 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t xml:space="preserve">Maltvej 58</t>
+          <t xml:space="preserve">Kærdalen 1</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
@@ -14151,20 +14151,20 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t xml:space="preserve">5039208</t>
+          <t xml:space="preserve">8097595</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J189">
-        <v>3216</v>
+        <v>1683</v>
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t xml:space="preserve">311288120</t>
+          <t xml:space="preserve">311289326</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
@@ -14174,7 +14174,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-11</t>
+          <t xml:space="preserve">2027-12-18</t>
         </is>
       </c>
       <c r="N189" t="inlineStr">
@@ -14216,17 +14216,17 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møllevænget 3</t>
+          <t xml:space="preserve">Kærdalen 1</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t xml:space="preserve">6622</t>
+          <t xml:space="preserve">6600</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t xml:space="preserve">5019884</t>
+          <t xml:space="preserve">8097596</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -14235,11 +14235,11 @@
         </is>
       </c>
       <c r="J190">
-        <v>442</v>
+        <v>1087</v>
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t xml:space="preserve">311288925</t>
+          <t xml:space="preserve">311289816</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
@@ -14249,7 +14249,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-15</t>
+          <t xml:space="preserve">2027-12-20</t>
         </is>
       </c>
       <c r="N190" t="inlineStr">
@@ -14291,7 +14291,7 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bakkevej 26</t>
+          <t xml:space="preserve">Kærdalen 1</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
@@ -14301,20 +14301,20 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t xml:space="preserve">8097595</t>
+          <t xml:space="preserve">8097597</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J191">
-        <v>1538</v>
+        <v>1367</v>
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289326</t>
+          <t xml:space="preserve">311289821</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
@@ -14324,7 +14324,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-18</t>
+          <t xml:space="preserve">2027-12-20</t>
         </is>
       </c>
       <c r="N191" t="inlineStr">
@@ -14366,30 +14366,30 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bakkevej 26</t>
+          <t xml:space="preserve">Vestergade 10</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t xml:space="preserve">6600</t>
+          <t xml:space="preserve">6622</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t xml:space="preserve">8097595</t>
+          <t xml:space="preserve">9197501</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J192">
-        <v>2669</v>
+        <v>706</v>
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289326</t>
+          <t xml:space="preserve">311290487</t>
         </is>
       </c>
       <c r="L192" t="inlineStr">
@@ -14399,7 +14399,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-18</t>
+          <t xml:space="preserve">2027-12-23</t>
         </is>
       </c>
       <c r="N192" t="inlineStr">
@@ -14441,30 +14441,30 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kærdalen 1</t>
+          <t xml:space="preserve">Vestergade 10</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t xml:space="preserve">6600</t>
+          <t xml:space="preserve">6622</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t xml:space="preserve">8097595</t>
+          <t xml:space="preserve">9197501</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="J193">
-        <v>1683</v>
+        <v>1125</v>
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289326</t>
+          <t xml:space="preserve">311290487</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
@@ -14474,7 +14474,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-18</t>
+          <t xml:space="preserve">2027-12-23</t>
         </is>
       </c>
       <c r="N193" t="inlineStr">
@@ -14516,30 +14516,30 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kærdalen 1</t>
+          <t xml:space="preserve">Vestergade 10</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t xml:space="preserve">6600</t>
+          <t xml:space="preserve">6622</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t xml:space="preserve">8097596</t>
+          <t xml:space="preserve">9197501</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="J194">
-        <v>1087</v>
+        <v>1045</v>
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289816</t>
+          <t xml:space="preserve">311290487</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
@@ -14549,7 +14549,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-20</t>
+          <t xml:space="preserve">2027-12-23</t>
         </is>
       </c>
       <c r="N194" t="inlineStr">
@@ -14591,30 +14591,30 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kærdalen 1</t>
+          <t xml:space="preserve">Vestergade 10</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t xml:space="preserve">6600</t>
+          <t xml:space="preserve">6622</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t xml:space="preserve">8097597</t>
+          <t xml:space="preserve">9197501</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="J195">
-        <v>1367</v>
+        <v>1150</v>
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289821</t>
+          <t xml:space="preserve">311290487</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
@@ -14624,7 +14624,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-20</t>
+          <t xml:space="preserve">2027-12-23</t>
         </is>
       </c>
       <c r="N195" t="inlineStr">
@@ -14681,11 +14681,11 @@
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="J196">
-        <v>706</v>
+        <v>296</v>
       </c>
       <c r="K196" t="inlineStr">
         <is>
@@ -14756,11 +14756,11 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J197">
-        <v>1125</v>
+        <v>645</v>
       </c>
       <c r="K197" t="inlineStr">
         <is>
@@ -14831,11 +14831,11 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J198">
-        <v>1045</v>
+        <v>668</v>
       </c>
       <c r="K198" t="inlineStr">
         <is>
@@ -14891,40 +14891,40 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergade 10</t>
+          <t xml:space="preserve">Skovvej 36</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t xml:space="preserve">6622</t>
+          <t xml:space="preserve">6600</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t xml:space="preserve">9197501</t>
+          <t xml:space="preserve">9691651</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J199">
-        <v>1150</v>
+        <v>265</v>
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t xml:space="preserve">311290487</t>
+          <t xml:space="preserve">311305978</t>
         </is>
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
         </is>
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-23</t>
+          <t xml:space="preserve">2028-03-30</t>
         </is>
       </c>
       <c r="N199" t="inlineStr">
@@ -14966,40 +14966,40 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergade 10</t>
+          <t xml:space="preserve">Skovvej 36</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t xml:space="preserve">6622</t>
+          <t xml:space="preserve">6600</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t xml:space="preserve">9197501</t>
+          <t xml:space="preserve">9691651</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J200">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t xml:space="preserve">311290487</t>
+          <t xml:space="preserve">311307544</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
         </is>
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-23</t>
+          <t xml:space="preserve">2028-04-10</t>
         </is>
       </c>
       <c r="N200" t="inlineStr">
@@ -15041,40 +15041,40 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergade 10</t>
+          <t xml:space="preserve">Skovvej 36</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t xml:space="preserve">6622</t>
+          <t xml:space="preserve">6600</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t xml:space="preserve">9197501</t>
+          <t xml:space="preserve">9691651</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J201">
-        <v>645</v>
+        <v>588</v>
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t xml:space="preserve">311290487</t>
+          <t xml:space="preserve">311307544</t>
         </is>
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
         </is>
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-23</t>
+          <t xml:space="preserve">2028-04-10</t>
         </is>
       </c>
       <c r="N201" t="inlineStr">
@@ -15116,40 +15116,40 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergade 10</t>
+          <t xml:space="preserve">Blomsterengen 43</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t xml:space="preserve">6622</t>
+          <t xml:space="preserve">6670</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t xml:space="preserve">9197501</t>
+          <t xml:space="preserve">9196503</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J202">
-        <v>668</v>
+        <v>271</v>
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t xml:space="preserve">311290487</t>
+          <t xml:space="preserve">311308332</t>
         </is>
       </c>
       <c r="L202" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
         </is>
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-23</t>
+          <t xml:space="preserve">2028-04-13</t>
         </is>
       </c>
       <c r="N202" t="inlineStr">
@@ -15191,30 +15191,30 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovvej 36</t>
+          <t xml:space="preserve">Skolegade 10</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t xml:space="preserve">6600</t>
+          <t xml:space="preserve">6650</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t xml:space="preserve">9691651</t>
+          <t xml:space="preserve">5032097</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J203">
-        <v>265</v>
+        <v>351</v>
       </c>
       <c r="K203" t="inlineStr">
         <is>
-          <t xml:space="preserve">311305978</t>
+          <t xml:space="preserve">311309220</t>
         </is>
       </c>
       <c r="L203" t="inlineStr">
@@ -15224,7 +15224,7 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-03-30</t>
+          <t xml:space="preserve">2028-04-18</t>
         </is>
       </c>
       <c r="N203" t="inlineStr">
@@ -15266,17 +15266,17 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovvej 36</t>
+          <t xml:space="preserve">Skolegade 7</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t xml:space="preserve">6600</t>
+          <t xml:space="preserve">6650</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t xml:space="preserve">9691651</t>
+          <t xml:space="preserve">9928625</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -15285,11 +15285,11 @@
         </is>
       </c>
       <c r="J204">
-        <v>293</v>
+        <v>825</v>
       </c>
       <c r="K204" t="inlineStr">
         <is>
-          <t xml:space="preserve">311307544</t>
+          <t xml:space="preserve">311309818</t>
         </is>
       </c>
       <c r="L204" t="inlineStr">
@@ -15299,7 +15299,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-04-10</t>
+          <t xml:space="preserve">2028-04-23</t>
         </is>
       </c>
       <c r="N204" t="inlineStr">
@@ -15341,7 +15341,7 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovvej 36</t>
+          <t xml:space="preserve">Rådhuspassagen 3</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
@@ -15351,7 +15351,7 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t xml:space="preserve">9691651</t>
+          <t xml:space="preserve">5041004</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -15360,21 +15360,21 @@
         </is>
       </c>
       <c r="J205">
-        <v>588</v>
+        <v>4946</v>
       </c>
       <c r="K205" t="inlineStr">
         <is>
-          <t xml:space="preserve">311307544</t>
+          <t xml:space="preserve">311395853</t>
         </is>
       </c>
       <c r="L205" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+          <t xml:space="preserve">EWII Energi A/S</t>
         </is>
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-04-10</t>
+          <t xml:space="preserve">2029-08-30</t>
         </is>
       </c>
       <c r="N205" t="inlineStr">
@@ -15416,17 +15416,17 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t xml:space="preserve">Blomsterengen 43</t>
+          <t xml:space="preserve">Vestergade 2</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t xml:space="preserve">6670</t>
+          <t xml:space="preserve">6600</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t xml:space="preserve">9196503</t>
+          <t xml:space="preserve">434528, 434529, 434530, 434531, 434532, 434533, 434878, 434885, 434534, 434535, 434536, 434537, 434870, 434872, 434873, 434874, 434875, 434876, 434877, 434879, 434880, 434881, 434882, 434883, 434884, 434886, 434887, 434888, 434889, 434890, 434891</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -15435,21 +15435,21 @@
         </is>
       </c>
       <c r="J206">
-        <v>271</v>
+        <v>6338</v>
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t xml:space="preserve">311308332</t>
+          <t xml:space="preserve">311402991</t>
         </is>
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+          <t xml:space="preserve">KEEN MILJØ &amp; ENERGIRÅDGIVNING ApS</t>
         </is>
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-04-13</t>
+          <t xml:space="preserve">2029-10-09</t>
         </is>
       </c>
       <c r="N206" t="inlineStr">
@@ -15491,17 +15491,17 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 10</t>
+          <t xml:space="preserve">Lindegade 10</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t xml:space="preserve">6650</t>
+          <t xml:space="preserve">6600</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t xml:space="preserve">5032097</t>
+          <t xml:space="preserve">5040356</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -15510,21 +15510,21 @@
         </is>
       </c>
       <c r="J207">
-        <v>351</v>
+        <v>673</v>
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t xml:space="preserve">311309220</t>
+          <t xml:space="preserve">311450533</t>
         </is>
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+          <t xml:space="preserve">KEEN MILJØ &amp; ENERGIRÅDGIVNING ApS</t>
         </is>
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-04-18</t>
+          <t xml:space="preserve">2030-07-20</t>
         </is>
       </c>
       <c r="N207" t="inlineStr">
@@ -15566,17 +15566,17 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 7</t>
+          <t xml:space="preserve">Højmarksvej 20</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t xml:space="preserve">6650</t>
+          <t xml:space="preserve">6670</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t xml:space="preserve">9928625</t>
+          <t xml:space="preserve">5036534</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -15585,11 +15585,11 @@
         </is>
       </c>
       <c r="J208">
-        <v>825</v>
+        <v>1800</v>
       </c>
       <c r="K208" t="inlineStr">
         <is>
-          <t xml:space="preserve">311309818</t>
+          <t xml:space="preserve">311529161</t>
         </is>
       </c>
       <c r="L208" t="inlineStr">
@@ -15599,7 +15599,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-04-23</t>
+          <t xml:space="preserve">2031-06-18</t>
         </is>
       </c>
       <c r="N208" t="inlineStr">
@@ -15641,40 +15641,40 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rådhuspassagen 3</t>
+          <t xml:space="preserve">Kirkepladsen 1</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t xml:space="preserve">6600</t>
+          <t xml:space="preserve">6660</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t xml:space="preserve">5041004</t>
+          <t xml:space="preserve">5196229</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J209">
-        <v>4946</v>
+        <v>1950</v>
       </c>
       <c r="K209" t="inlineStr">
         <is>
-          <t xml:space="preserve">311395853</t>
+          <t xml:space="preserve">311529164</t>
         </is>
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t xml:space="preserve">EWII Energi A/S</t>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
         </is>
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-08-30</t>
+          <t xml:space="preserve">2031-06-18</t>
         </is>
       </c>
       <c r="N209" t="inlineStr">
@@ -15716,17 +15716,17 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergade 2</t>
+          <t xml:space="preserve">Krygersvej 2</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t xml:space="preserve">6600</t>
+          <t xml:space="preserve">6630</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t xml:space="preserve">434528, 434529, 434530, 434531, 434532, 434533, 434878, 434885, 434534, 434535, 434536, 434537, 434870, 434872, 434873, 434874, 434875, 434876, 434877, 434879, 434880, 434881, 434882, 434883, 434884, 434886, 434887, 434888, 434889, 434890, 434891</t>
+          <t xml:space="preserve">8309304</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -15735,21 +15735,21 @@
         </is>
       </c>
       <c r="J210">
-        <v>6338</v>
+        <v>4954</v>
       </c>
       <c r="K210" t="inlineStr">
         <is>
-          <t xml:space="preserve">311402991</t>
+          <t xml:space="preserve">311529162</t>
         </is>
       </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t xml:space="preserve">KEEN MILJØ &amp; ENERGIRÅDGIVNING ApS</t>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
         </is>
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-10-09</t>
+          <t xml:space="preserve">2031-06-18</t>
         </is>
       </c>
       <c r="N210" t="inlineStr">
@@ -15791,17 +15791,17 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lindegade 10</t>
+          <t xml:space="preserve">Stadionvej 15</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t xml:space="preserve">6600</t>
+          <t xml:space="preserve">6650</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t xml:space="preserve">5040356</t>
+          <t xml:space="preserve">1484897</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -15810,21 +15810,21 @@
         </is>
       </c>
       <c r="J211">
-        <v>673</v>
+        <v>2189</v>
       </c>
       <c r="K211" t="inlineStr">
         <is>
-          <t xml:space="preserve">311450533</t>
+          <t xml:space="preserve">311529163</t>
         </is>
       </c>
       <c r="L211" t="inlineStr">
         <is>
-          <t xml:space="preserve">KEEN MILJØ &amp; ENERGIRÅDGIVNING ApS</t>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
         </is>
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-07-20</t>
+          <t xml:space="preserve">2031-06-18</t>
         </is>
       </c>
       <c r="N211" t="inlineStr">
@@ -15866,17 +15866,17 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t xml:space="preserve">Højmarksvej 20</t>
+          <t xml:space="preserve">Skodborg Nørregade 6</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t xml:space="preserve">6670</t>
+          <t xml:space="preserve">6630</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t xml:space="preserve">5036534</t>
+          <t xml:space="preserve">308654</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -15885,21 +15885,21 @@
         </is>
       </c>
       <c r="J212">
-        <v>1800</v>
+        <v>963</v>
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t xml:space="preserve">311529161</t>
+          <t xml:space="preserve">311533232</t>
         </is>
       </c>
       <c r="L212" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-06-18</t>
+          <t xml:space="preserve">2031-07-02</t>
         </is>
       </c>
       <c r="N212" t="inlineStr">
@@ -15941,17 +15941,17 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkepladsen 1</t>
+          <t xml:space="preserve">Rødding Engvej 3</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t xml:space="preserve">6660</t>
+          <t xml:space="preserve">6630</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t xml:space="preserve">5196229</t>
+          <t xml:space="preserve">5197937</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -15960,11 +15960,11 @@
         </is>
       </c>
       <c r="J213">
-        <v>1950</v>
+        <v>1070</v>
       </c>
       <c r="K213" t="inlineStr">
         <is>
-          <t xml:space="preserve">311529164</t>
+          <t xml:space="preserve">311534227</t>
         </is>
       </c>
       <c r="L213" t="inlineStr">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-06-18</t>
+          <t xml:space="preserve">2031-07-07</t>
         </is>
       </c>
       <c r="N213" t="inlineStr">
@@ -16016,7 +16016,7 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t xml:space="preserve">Krygersvej 2</t>
+          <t xml:space="preserve">Rødding Engvej 3</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
@@ -16026,20 +16026,20 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t xml:space="preserve">8309304</t>
+          <t xml:space="preserve">5197937</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J214">
-        <v>4954</v>
+        <v>326</v>
       </c>
       <c r="K214" t="inlineStr">
         <is>
-          <t xml:space="preserve">311529162</t>
+          <t xml:space="preserve">311534227</t>
         </is>
       </c>
       <c r="L214" t="inlineStr">
@@ -16049,7 +16049,7 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-06-18</t>
+          <t xml:space="preserve">2031-07-07</t>
         </is>
       </c>
       <c r="N214" t="inlineStr">
@@ -16091,17 +16091,17 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionvej 15</t>
+          <t xml:space="preserve">Industrivej Vest 18</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t xml:space="preserve">6650</t>
+          <t xml:space="preserve">6600</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t xml:space="preserve">1484897</t>
+          <t xml:space="preserve">10156994</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -16110,21 +16110,21 @@
         </is>
       </c>
       <c r="J215">
-        <v>2189</v>
+        <v>325</v>
       </c>
       <c r="K215" t="inlineStr">
         <is>
-          <t xml:space="preserve">311529163</t>
+          <t xml:space="preserve">311535979</t>
         </is>
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+          <t xml:space="preserve">Ankersen ApS</t>
         </is>
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-06-18</t>
+          <t xml:space="preserve">2031-07-14</t>
         </is>
       </c>
       <c r="N215" t="inlineStr">
@@ -16166,17 +16166,17 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skodborg Nørregade 6</t>
+          <t xml:space="preserve">Hovborgvej 1</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t xml:space="preserve">6630</t>
+          <t xml:space="preserve">6650</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t xml:space="preserve">308654</t>
+          <t xml:space="preserve">5037992</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -16185,21 +16185,21 @@
         </is>
       </c>
       <c r="J216">
-        <v>963</v>
+        <v>134</v>
       </c>
       <c r="K216" t="inlineStr">
         <is>
-          <t xml:space="preserve">311533232</t>
+          <t xml:space="preserve">311540206</t>
         </is>
       </c>
       <c r="L216" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
         </is>
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-07-02</t>
+          <t xml:space="preserve">2031-08-11</t>
         </is>
       </c>
       <c r="N216" t="inlineStr">
@@ -16241,30 +16241,30 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rødding Engvej 3</t>
+          <t xml:space="preserve">Hovborgvej 1</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t xml:space="preserve">6630</t>
+          <t xml:space="preserve">6650</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t xml:space="preserve">5197937</t>
+          <t xml:space="preserve">5037992</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J217">
-        <v>1070</v>
+        <v>294</v>
       </c>
       <c r="K217" t="inlineStr">
         <is>
-          <t xml:space="preserve">311534227</t>
+          <t xml:space="preserve">311540206</t>
         </is>
       </c>
       <c r="L217" t="inlineStr">
@@ -16274,7 +16274,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-07-07</t>
+          <t xml:space="preserve">2031-08-11</t>
         </is>
       </c>
       <c r="N217" t="inlineStr">
@@ -16316,30 +16316,30 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rødding Engvej 3</t>
+          <t xml:space="preserve">Hovborgvej 1</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t xml:space="preserve">6630</t>
+          <t xml:space="preserve">6650</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t xml:space="preserve">5197937</t>
+          <t xml:space="preserve">5037992</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J218">
-        <v>326</v>
+        <v>1558</v>
       </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t xml:space="preserve">311534227</t>
+          <t xml:space="preserve">311540206</t>
         </is>
       </c>
       <c r="L218" t="inlineStr">
@@ -16349,7 +16349,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-07-07</t>
+          <t xml:space="preserve">2031-08-11</t>
         </is>
       </c>
       <c r="N218" t="inlineStr">
@@ -16391,40 +16391,40 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t xml:space="preserve">Industrivej Vest 18</t>
+          <t xml:space="preserve">Hovborgvej 1</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t xml:space="preserve">6600</t>
+          <t xml:space="preserve">6650</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t xml:space="preserve">10156994</t>
+          <t xml:space="preserve">5037992</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J219">
-        <v>325</v>
+        <v>348</v>
       </c>
       <c r="K219" t="inlineStr">
         <is>
-          <t xml:space="preserve">311535979</t>
+          <t xml:space="preserve">311540206</t>
         </is>
       </c>
       <c r="L219" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ankersen ApS</t>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
         </is>
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-07-14</t>
+          <t xml:space="preserve">2031-08-11</t>
         </is>
       </c>
       <c r="N219" t="inlineStr">
@@ -16466,7 +16466,7 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovborgvej 1</t>
+          <t xml:space="preserve">Skolegade 2</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
@@ -16476,7 +16476,7 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t xml:space="preserve">5037992</t>
+          <t xml:space="preserve">5032058</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -16485,11 +16485,11 @@
         </is>
       </c>
       <c r="J220">
-        <v>134</v>
+        <v>2285</v>
       </c>
       <c r="K220" t="inlineStr">
         <is>
-          <t xml:space="preserve">311540206</t>
+          <t xml:space="preserve">311541332</t>
         </is>
       </c>
       <c r="L220" t="inlineStr">
@@ -16499,7 +16499,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-11</t>
+          <t xml:space="preserve">2031-08-17</t>
         </is>
       </c>
       <c r="N220" t="inlineStr">
@@ -16541,7 +16541,7 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovborgvej 1</t>
+          <t xml:space="preserve">Skolegade 2</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
@@ -16551,7 +16551,7 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t xml:space="preserve">5037992</t>
+          <t xml:space="preserve">5032058</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -16560,11 +16560,11 @@
         </is>
       </c>
       <c r="J221">
-        <v>294</v>
+        <v>285</v>
       </c>
       <c r="K221" t="inlineStr">
         <is>
-          <t xml:space="preserve">311540206</t>
+          <t xml:space="preserve">311541332</t>
         </is>
       </c>
       <c r="L221" t="inlineStr">
@@ -16574,7 +16574,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-11</t>
+          <t xml:space="preserve">2031-08-17</t>
         </is>
       </c>
       <c r="N221" t="inlineStr">
@@ -16616,7 +16616,7 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovborgvej 1</t>
+          <t xml:space="preserve">Skolegade 2</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
@@ -16626,7 +16626,7 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t xml:space="preserve">5037992</t>
+          <t xml:space="preserve">5032058</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
@@ -16635,11 +16635,11 @@
         </is>
       </c>
       <c r="J222">
-        <v>1558</v>
+        <v>649</v>
       </c>
       <c r="K222" t="inlineStr">
         <is>
-          <t xml:space="preserve">311540206</t>
+          <t xml:space="preserve">311541332</t>
         </is>
       </c>
       <c r="L222" t="inlineStr">
@@ -16649,7 +16649,7 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-11</t>
+          <t xml:space="preserve">2031-08-17</t>
         </is>
       </c>
       <c r="N222" t="inlineStr">
@@ -16691,7 +16691,7 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovborgvej 1</t>
+          <t xml:space="preserve">Skolegade 2</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
@@ -16701,7 +16701,7 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t xml:space="preserve">5037992</t>
+          <t xml:space="preserve">5032058</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -16710,11 +16710,11 @@
         </is>
       </c>
       <c r="J223">
-        <v>348</v>
+        <v>1337</v>
       </c>
       <c r="K223" t="inlineStr">
         <is>
-          <t xml:space="preserve">311540206</t>
+          <t xml:space="preserve">311541332</t>
         </is>
       </c>
       <c r="L223" t="inlineStr">
@@ -16724,7 +16724,7 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-11</t>
+          <t xml:space="preserve">2031-08-17</t>
         </is>
       </c>
       <c r="N223" t="inlineStr">
@@ -16781,11 +16781,11 @@
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J224">
-        <v>2285</v>
+        <v>461</v>
       </c>
       <c r="K224" t="inlineStr">
         <is>
@@ -16856,11 +16856,11 @@
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J225">
-        <v>285</v>
+        <v>396</v>
       </c>
       <c r="K225" t="inlineStr">
         <is>
@@ -16916,30 +16916,30 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 2</t>
+          <t xml:space="preserve">Østergade 28</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t xml:space="preserve">6650</t>
+          <t xml:space="preserve">6630</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t xml:space="preserve">5032058</t>
+          <t xml:space="preserve">5198538</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J226">
-        <v>649</v>
+        <v>2208</v>
       </c>
       <c r="K226" t="inlineStr">
         <is>
-          <t xml:space="preserve">311541332</t>
+          <t xml:space="preserve">311543399</t>
         </is>
       </c>
       <c r="L226" t="inlineStr">
@@ -16949,7 +16949,7 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-17</t>
+          <t xml:space="preserve">2031-08-26</t>
         </is>
       </c>
       <c r="N226" t="inlineStr">
@@ -16991,30 +16991,30 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 2</t>
+          <t xml:space="preserve">Rytterdam 1C</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t xml:space="preserve">6650</t>
+          <t xml:space="preserve">6630</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t xml:space="preserve">5032058</t>
+          <t xml:space="preserve">9252176</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J227">
-        <v>1337</v>
+        <v>353</v>
       </c>
       <c r="K227" t="inlineStr">
         <is>
-          <t xml:space="preserve">311541332</t>
+          <t xml:space="preserve">311546545</t>
         </is>
       </c>
       <c r="L227" t="inlineStr">
@@ -17024,7 +17024,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-17</t>
+          <t xml:space="preserve">2031-09-08</t>
         </is>
       </c>
       <c r="N227" t="inlineStr">
@@ -17066,30 +17066,30 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 2</t>
+          <t xml:space="preserve">Rytterdam 9</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t xml:space="preserve">6650</t>
+          <t xml:space="preserve">6630</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t xml:space="preserve">5032058</t>
+          <t xml:space="preserve">9252176</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J228">
-        <v>461</v>
+        <v>8186</v>
       </c>
       <c r="K228" t="inlineStr">
         <is>
-          <t xml:space="preserve">311541332</t>
+          <t xml:space="preserve">311546545</t>
         </is>
       </c>
       <c r="L228" t="inlineStr">
@@ -17099,7 +17099,7 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-17</t>
+          <t xml:space="preserve">2031-09-08</t>
         </is>
       </c>
       <c r="N228" t="inlineStr">
@@ -17141,30 +17141,30 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 2</t>
+          <t xml:space="preserve">Rytterdam 9</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t xml:space="preserve">6650</t>
+          <t xml:space="preserve">6630</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t xml:space="preserve">5032058</t>
+          <t xml:space="preserve">9252176</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J229">
-        <v>396</v>
+        <v>586</v>
       </c>
       <c r="K229" t="inlineStr">
         <is>
-          <t xml:space="preserve">311541332</t>
+          <t xml:space="preserve">311546545</t>
         </is>
       </c>
       <c r="L229" t="inlineStr">
@@ -17174,7 +17174,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-17</t>
+          <t xml:space="preserve">2031-09-08</t>
         </is>
       </c>
       <c r="N229" t="inlineStr">
@@ -17216,7 +17216,7 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østergade 28</t>
+          <t xml:space="preserve">Rytterdam 9</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
@@ -17226,20 +17226,20 @@
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t xml:space="preserve">5198538</t>
+          <t xml:space="preserve">9252176</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J230">
-        <v>2208</v>
+        <v>665</v>
       </c>
       <c r="K230" t="inlineStr">
         <is>
-          <t xml:space="preserve">311543399</t>
+          <t xml:space="preserve">311546545</t>
         </is>
       </c>
       <c r="L230" t="inlineStr">
@@ -17249,7 +17249,7 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-26</t>
+          <t xml:space="preserve">2031-09-08</t>
         </is>
       </c>
       <c r="N230" t="inlineStr">
@@ -17291,17 +17291,17 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rytterdam 1C</t>
+          <t xml:space="preserve">Åttevej 8</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t xml:space="preserve">6630</t>
+          <t xml:space="preserve">6683</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t xml:space="preserve">9252176</t>
+          <t xml:space="preserve">5034272</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
@@ -17310,11 +17310,11 @@
         </is>
       </c>
       <c r="J231">
-        <v>353</v>
+        <v>1625</v>
       </c>
       <c r="K231" t="inlineStr">
         <is>
-          <t xml:space="preserve">311546545</t>
+          <t xml:space="preserve">311547050</t>
         </is>
       </c>
       <c r="L231" t="inlineStr">
@@ -17324,7 +17324,7 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-08</t>
+          <t xml:space="preserve">2031-09-09</t>
         </is>
       </c>
       <c r="N231" t="inlineStr">
@@ -17366,17 +17366,17 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rytterdam 9</t>
+          <t xml:space="preserve">Åttevej 8</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t xml:space="preserve">6630</t>
+          <t xml:space="preserve">6683</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t xml:space="preserve">9252176</t>
+          <t xml:space="preserve">5034272</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
@@ -17385,11 +17385,11 @@
         </is>
       </c>
       <c r="J232">
-        <v>8186</v>
+        <v>339</v>
       </c>
       <c r="K232" t="inlineStr">
         <is>
-          <t xml:space="preserve">311546545</t>
+          <t xml:space="preserve">311547065</t>
         </is>
       </c>
       <c r="L232" t="inlineStr">
@@ -17399,7 +17399,7 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-08</t>
+          <t xml:space="preserve">2031-09-09</t>
         </is>
       </c>
       <c r="N232" t="inlineStr">
@@ -17441,30 +17441,30 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rytterdam 9</t>
+          <t xml:space="preserve">Åttevej 8</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t xml:space="preserve">6630</t>
+          <t xml:space="preserve">6683</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t xml:space="preserve">9252176</t>
+          <t xml:space="preserve">5034272</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J233">
-        <v>586</v>
+        <v>218</v>
       </c>
       <c r="K233" t="inlineStr">
         <is>
-          <t xml:space="preserve">311546545</t>
+          <t xml:space="preserve">311547065</t>
         </is>
       </c>
       <c r="L233" t="inlineStr">
@@ -17474,7 +17474,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-08</t>
+          <t xml:space="preserve">2031-09-09</t>
         </is>
       </c>
       <c r="N233" t="inlineStr">
@@ -17516,30 +17516,30 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rytterdam 9</t>
+          <t xml:space="preserve">Åttevej 8</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t xml:space="preserve">6630</t>
+          <t xml:space="preserve">6683</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t xml:space="preserve">9252176</t>
+          <t xml:space="preserve">5034272</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J234">
-        <v>665</v>
+        <v>348</v>
       </c>
       <c r="K234" t="inlineStr">
         <is>
-          <t xml:space="preserve">311546545</t>
+          <t xml:space="preserve">311547018</t>
         </is>
       </c>
       <c r="L234" t="inlineStr">
@@ -17549,7 +17549,7 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-08</t>
+          <t xml:space="preserve">2031-09-09</t>
         </is>
       </c>
       <c r="N234" t="inlineStr">
@@ -17591,17 +17591,17 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t xml:space="preserve">Åttevej 8</t>
+          <t xml:space="preserve">Parkvej 4</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t xml:space="preserve">6683</t>
+          <t xml:space="preserve">6630</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t xml:space="preserve">5034272</t>
+          <t xml:space="preserve">5198848</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
@@ -17610,11 +17610,11 @@
         </is>
       </c>
       <c r="J235">
-        <v>1625</v>
+        <v>950</v>
       </c>
       <c r="K235" t="inlineStr">
         <is>
-          <t xml:space="preserve">311547050</t>
+          <t xml:space="preserve">311572718</t>
         </is>
       </c>
       <c r="L235" t="inlineStr">
@@ -17624,7 +17624,7 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-09</t>
+          <t xml:space="preserve">2031-09-24</t>
         </is>
       </c>
       <c r="N235" t="inlineStr">
@@ -17666,30 +17666,30 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t xml:space="preserve">Åttevej 8</t>
+          <t xml:space="preserve">Højmarksvej 16</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t xml:space="preserve">6683</t>
+          <t xml:space="preserve">6670</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t xml:space="preserve">5034272</t>
+          <t xml:space="preserve">5036460</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J236">
-        <v>339</v>
+        <v>1255</v>
       </c>
       <c r="K236" t="inlineStr">
         <is>
-          <t xml:space="preserve">311547065</t>
+          <t xml:space="preserve">311560309</t>
         </is>
       </c>
       <c r="L236" t="inlineStr">
@@ -17699,7 +17699,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-09</t>
+          <t xml:space="preserve">2031-11-08</t>
         </is>
       </c>
       <c r="N236" t="inlineStr">
@@ -17741,30 +17741,30 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t xml:space="preserve">Åttevej 8</t>
+          <t xml:space="preserve">Højmarksvej 16</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t xml:space="preserve">6683</t>
+          <t xml:space="preserve">6670</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t xml:space="preserve">5034272</t>
+          <t xml:space="preserve">5036460</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J237">
-        <v>218</v>
+        <v>1422</v>
       </c>
       <c r="K237" t="inlineStr">
         <is>
-          <t xml:space="preserve">311547065</t>
+          <t xml:space="preserve">311560309</t>
         </is>
       </c>
       <c r="L237" t="inlineStr">
@@ -17774,7 +17774,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-09</t>
+          <t xml:space="preserve">2031-11-08</t>
         </is>
       </c>
       <c r="N237" t="inlineStr">
@@ -17816,30 +17816,30 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t xml:space="preserve">Åttevej 8</t>
+          <t xml:space="preserve">Højmarksvej 16</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t xml:space="preserve">6683</t>
+          <t xml:space="preserve">6670</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t xml:space="preserve">5034272</t>
+          <t xml:space="preserve">5036460</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">20</t>
         </is>
       </c>
       <c r="J238">
-        <v>348</v>
+        <v>962</v>
       </c>
       <c r="K238" t="inlineStr">
         <is>
-          <t xml:space="preserve">311547018</t>
+          <t xml:space="preserve">311560309</t>
         </is>
       </c>
       <c r="L238" t="inlineStr">
@@ -17849,7 +17849,7 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-09</t>
+          <t xml:space="preserve">2031-11-08</t>
         </is>
       </c>
       <c r="N238" t="inlineStr">
@@ -17891,30 +17891,30 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parkvej 4</t>
+          <t xml:space="preserve">Højmarksvej 16</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t xml:space="preserve">6630</t>
+          <t xml:space="preserve">6670</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t xml:space="preserve">5198848</t>
+          <t xml:space="preserve">5036460</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J239">
-        <v>950</v>
+        <v>1499</v>
       </c>
       <c r="K239" t="inlineStr">
         <is>
-          <t xml:space="preserve">311572718</t>
+          <t xml:space="preserve">311560309</t>
         </is>
       </c>
       <c r="L239" t="inlineStr">
@@ -17924,7 +17924,7 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-24</t>
+          <t xml:space="preserve">2031-11-08</t>
         </is>
       </c>
       <c r="N239" t="inlineStr">
@@ -17981,11 +17981,11 @@
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J240">
-        <v>1255</v>
+        <v>1232</v>
       </c>
       <c r="K240" t="inlineStr">
         <is>
@@ -18056,11 +18056,11 @@
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J241">
-        <v>1422</v>
+        <v>838</v>
       </c>
       <c r="K241" t="inlineStr">
         <is>
@@ -18131,11 +18131,11 @@
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J242">
-        <v>962</v>
+        <v>587</v>
       </c>
       <c r="K242" t="inlineStr">
         <is>
@@ -18206,11 +18206,11 @@
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J243">
-        <v>1499</v>
+        <v>412</v>
       </c>
       <c r="K243" t="inlineStr">
         <is>
@@ -18266,30 +18266,30 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t xml:space="preserve">Højmarksvej 16</t>
+          <t xml:space="preserve">Nørretoft 2</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t xml:space="preserve">6670</t>
+          <t xml:space="preserve">6660</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t xml:space="preserve">5036460</t>
+          <t xml:space="preserve">5196345</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J244">
-        <v>1232</v>
+        <v>226</v>
       </c>
       <c r="K244" t="inlineStr">
         <is>
-          <t xml:space="preserve">311560309</t>
+          <t xml:space="preserve">311560551</t>
         </is>
       </c>
       <c r="L244" t="inlineStr">
@@ -18299,7 +18299,7 @@
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-08</t>
+          <t xml:space="preserve">2031-11-09</t>
         </is>
       </c>
       <c r="N244" t="inlineStr">
@@ -18341,17 +18341,17 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t xml:space="preserve">Højmarksvej 16</t>
+          <t xml:space="preserve">Nørretoft 2</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t xml:space="preserve">6670</t>
+          <t xml:space="preserve">6660</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t xml:space="preserve">5036460</t>
+          <t xml:space="preserve">5196345</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
@@ -18360,11 +18360,11 @@
         </is>
       </c>
       <c r="J245">
-        <v>838</v>
+        <v>213</v>
       </c>
       <c r="K245" t="inlineStr">
         <is>
-          <t xml:space="preserve">311560309</t>
+          <t xml:space="preserve">311560551</t>
         </is>
       </c>
       <c r="L245" t="inlineStr">
@@ -18374,7 +18374,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-08</t>
+          <t xml:space="preserve">2031-11-09</t>
         </is>
       </c>
       <c r="N245" t="inlineStr">
@@ -18416,40 +18416,40 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t xml:space="preserve">Højmarksvej 16</t>
+          <t xml:space="preserve">Knudevejen 17B</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t xml:space="preserve">6670</t>
+          <t xml:space="preserve">6600</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t xml:space="preserve">5036460</t>
+          <t xml:space="preserve">7813581</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">50</t>
         </is>
       </c>
       <c r="J246">
-        <v>587</v>
+        <v>103</v>
       </c>
       <c r="K246" t="inlineStr">
         <is>
-          <t xml:space="preserve">311560309</t>
+          <t xml:space="preserve">311660921</t>
         </is>
       </c>
       <c r="L246" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+          <t xml:space="preserve">Murbyg ApS</t>
         </is>
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-08</t>
+          <t xml:space="preserve">2033-02-17</t>
         </is>
       </c>
       <c r="N246" t="inlineStr">
@@ -18491,40 +18491,40 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t xml:space="preserve">Højmarksvej 16</t>
+          <t xml:space="preserve">Knudevejen 17B</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t xml:space="preserve">6670</t>
+          <t xml:space="preserve">6600</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t xml:space="preserve">5036460</t>
+          <t xml:space="preserve">7813581</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">69</t>
         </is>
       </c>
       <c r="J247">
-        <v>412</v>
+        <v>328</v>
       </c>
       <c r="K247" t="inlineStr">
         <is>
-          <t xml:space="preserve">311560309</t>
+          <t xml:space="preserve">311660921</t>
         </is>
       </c>
       <c r="L247" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+          <t xml:space="preserve">Murbyg ApS</t>
         </is>
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-08</t>
+          <t xml:space="preserve">2033-02-17</t>
         </is>
       </c>
       <c r="N247" t="inlineStr">
@@ -18566,40 +18566,40 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørretoft 2</t>
+          <t xml:space="preserve">Borgergade 110</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t xml:space="preserve">6660</t>
+          <t xml:space="preserve">6752</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t xml:space="preserve">5196345</t>
+          <t xml:space="preserve">310746</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J248">
-        <v>226</v>
+        <v>912</v>
       </c>
       <c r="K248" t="inlineStr">
         <is>
-          <t xml:space="preserve">311560551</t>
+          <t xml:space="preserve">311730609</t>
         </is>
       </c>
       <c r="L248" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-09</t>
+          <t xml:space="preserve">2033-12-20</t>
         </is>
       </c>
       <c r="N248" t="inlineStr">
@@ -18641,40 +18641,40 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørretoft 2</t>
+          <t xml:space="preserve">Drejervej 7</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t xml:space="preserve">6660</t>
+          <t xml:space="preserve">6600</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t xml:space="preserve">5196345</t>
+          <t xml:space="preserve">5043606</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J249">
-        <v>213</v>
+        <v>2188</v>
       </c>
       <c r="K249" t="inlineStr">
         <is>
-          <t xml:space="preserve">311560551</t>
+          <t xml:space="preserve">311740342</t>
         </is>
       </c>
       <c r="L249" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-09</t>
+          <t xml:space="preserve">2034-02-21</t>
         </is>
       </c>
       <c r="N249" t="inlineStr">
@@ -18716,7 +18716,7 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t xml:space="preserve">Knudevejen 17A</t>
+          <t xml:space="preserve">Drejervej 9</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
@@ -18726,30 +18726,30 @@
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t xml:space="preserve">7813581</t>
+          <t xml:space="preserve">5043606</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J250">
-        <v>386</v>
+        <v>182</v>
       </c>
       <c r="K250" t="inlineStr">
         <is>
-          <t xml:space="preserve">311660921</t>
+          <t xml:space="preserve">311740342</t>
         </is>
       </c>
       <c r="L250" t="inlineStr">
         <is>
-          <t xml:space="preserve">Murbyg ApS</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-02-17</t>
+          <t xml:space="preserve">2034-02-21</t>
         </is>
       </c>
       <c r="N250" t="inlineStr">
@@ -18791,7 +18791,7 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t xml:space="preserve">Knudevejen 17B</t>
+          <t xml:space="preserve">Rugholmvej 16</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
@@ -18801,7 +18801,7 @@
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t xml:space="preserve">7813581</t>
+          <t xml:space="preserve">100002769</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
@@ -18810,21 +18810,21 @@
         </is>
       </c>
       <c r="J251">
-        <v>386</v>
+        <v>294</v>
       </c>
       <c r="K251" t="inlineStr">
         <is>
-          <t xml:space="preserve">311660921</t>
+          <t xml:space="preserve">311791576</t>
         </is>
       </c>
       <c r="L251" t="inlineStr">
         <is>
-          <t xml:space="preserve">Murbyg ApS</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-02-17</t>
+          <t xml:space="preserve">2034-10-15</t>
         </is>
       </c>
       <c r="N251" t="inlineStr">
@@ -18866,7 +18866,7 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t xml:space="preserve">Knudevejen 17B</t>
+          <t xml:space="preserve">Rugholmvej 16</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
@@ -18876,30 +18876,30 @@
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t xml:space="preserve">7813581</t>
+          <t xml:space="preserve">100002769</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t xml:space="preserve">50</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J252">
-        <v>103</v>
+        <v>158</v>
       </c>
       <c r="K252" t="inlineStr">
         <is>
-          <t xml:space="preserve">311660921</t>
+          <t xml:space="preserve">311791576</t>
         </is>
       </c>
       <c r="L252" t="inlineStr">
         <is>
-          <t xml:space="preserve">Murbyg ApS</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-02-17</t>
+          <t xml:space="preserve">2034-10-15</t>
         </is>
       </c>
       <c r="N252" t="inlineStr">
@@ -18941,40 +18941,40 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t xml:space="preserve">Knudevejen 17B</t>
+          <t xml:space="preserve">Vestergade 19</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t xml:space="preserve">6600</t>
+          <t xml:space="preserve">6670</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t xml:space="preserve">7813581</t>
+          <t xml:space="preserve">5035619</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t xml:space="preserve">61</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J253">
-        <v>130</v>
+        <v>315</v>
       </c>
       <c r="K253" t="inlineStr">
         <is>
-          <t xml:space="preserve">311660921</t>
+          <t xml:space="preserve">311814507</t>
         </is>
       </c>
       <c r="L253" t="inlineStr">
         <is>
-          <t xml:space="preserve">Murbyg ApS</t>
+          <t xml:space="preserve">OBH</t>
         </is>
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-02-17</t>
+          <t xml:space="preserve">2035-02-28</t>
         </is>
       </c>
       <c r="N253" t="inlineStr">
@@ -19016,40 +19016,40 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t xml:space="preserve">Knudevejen 17B</t>
+          <t xml:space="preserve">Højmarksvej 18</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t xml:space="preserve">6600</t>
+          <t xml:space="preserve">6670</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t xml:space="preserve">7813581</t>
+          <t xml:space="preserve">5036533</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t xml:space="preserve">69</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J254">
-        <v>328</v>
+        <v>2243</v>
       </c>
       <c r="K254" t="inlineStr">
         <is>
-          <t xml:space="preserve">311660921</t>
+          <t xml:space="preserve">311894920</t>
         </is>
       </c>
       <c r="L254" t="inlineStr">
         <is>
-          <t xml:space="preserve">Murbyg ApS</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-02-17</t>
+          <t xml:space="preserve">2036-04-17</t>
         </is>
       </c>
       <c r="N254" t="inlineStr">
@@ -19091,40 +19091,40 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t xml:space="preserve">Borgergade 110</t>
+          <t xml:space="preserve">Højmarksvej 18</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t xml:space="preserve">6752</t>
+          <t xml:space="preserve">6670</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t xml:space="preserve">310746</t>
+          <t xml:space="preserve">5036533</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J255">
-        <v>912</v>
+        <v>3900</v>
       </c>
       <c r="K255" t="inlineStr">
         <is>
-          <t xml:space="preserve">311730609</t>
+          <t xml:space="preserve">311894909</t>
         </is>
       </c>
       <c r="L255" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-20</t>
+          <t xml:space="preserve">2036-04-17</t>
         </is>
       </c>
       <c r="N255" t="inlineStr">
@@ -19166,40 +19166,40 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t xml:space="preserve">Drejervej 7</t>
+          <t xml:space="preserve">Møllevænget 5</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t xml:space="preserve">6600</t>
+          <t xml:space="preserve">6622</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t xml:space="preserve">5043606</t>
+          <t xml:space="preserve">737305, 5019907</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J256">
-        <v>2188</v>
+        <v>2050</v>
       </c>
       <c r="K256" t="inlineStr">
         <is>
-          <t xml:space="preserve">311740342</t>
+          <t xml:space="preserve">311894926</t>
         </is>
       </c>
       <c r="L256" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-02-21</t>
+          <t xml:space="preserve">2036-04-17</t>
         </is>
       </c>
       <c r="N256" t="inlineStr">
@@ -19241,40 +19241,40 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t xml:space="preserve">Drejervej 9</t>
+          <t xml:space="preserve">Ørstedvej 10</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t xml:space="preserve">6600</t>
+          <t xml:space="preserve">6630</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t xml:space="preserve">5043606</t>
+          <t xml:space="preserve">737335, 5186260</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J257">
-        <v>182</v>
+        <v>537</v>
       </c>
       <c r="K257" t="inlineStr">
         <is>
-          <t xml:space="preserve">311740342</t>
+          <t xml:space="preserve">311894879</t>
         </is>
       </c>
       <c r="L257" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-02-21</t>
+          <t xml:space="preserve">2036-04-17</t>
         </is>
       </c>
       <c r="N257" t="inlineStr">
@@ -19316,40 +19316,40 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rugholmvej 16</t>
+          <t xml:space="preserve">Stadionvej 2A</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t xml:space="preserve">6600</t>
+          <t xml:space="preserve">6752</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t xml:space="preserve">100002769</t>
+          <t xml:space="preserve">737383, 5045451</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J258">
-        <v>294</v>
+        <v>423</v>
       </c>
       <c r="K258" t="inlineStr">
         <is>
-          <t xml:space="preserve">311791576</t>
+          <t xml:space="preserve">311895815</t>
         </is>
       </c>
       <c r="L258" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-10-15</t>
+          <t xml:space="preserve">2036-04-22</t>
         </is>
       </c>
       <c r="N258" t="inlineStr">
@@ -19391,40 +19391,40 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rugholmvej 16</t>
+          <t xml:space="preserve">Stadionvej 2A</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t xml:space="preserve">6600</t>
+          <t xml:space="preserve">6752</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t xml:space="preserve">100002769</t>
+          <t xml:space="preserve">737383, 5045451</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J259">
-        <v>158</v>
+        <v>1665</v>
       </c>
       <c r="K259" t="inlineStr">
         <is>
-          <t xml:space="preserve">311791576</t>
+          <t xml:space="preserve">311896169</t>
         </is>
       </c>
       <c r="L259" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-10-15</t>
+          <t xml:space="preserve">2036-04-23</t>
         </is>
       </c>
       <c r="N259" t="inlineStr">
@@ -19466,40 +19466,40 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergade 19</t>
+          <t xml:space="preserve">Stadionvej 2A</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t xml:space="preserve">6670</t>
+          <t xml:space="preserve">6752</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t xml:space="preserve">5035619</t>
+          <t xml:space="preserve">737383, 5045451</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J260">
-        <v>315</v>
+        <v>273</v>
       </c>
       <c r="K260" t="inlineStr">
         <is>
-          <t xml:space="preserve">311814507</t>
+          <t xml:space="preserve">311896606</t>
         </is>
       </c>
       <c r="L260" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-02-28</t>
+          <t xml:space="preserve">2036-04-24</t>
         </is>
       </c>
       <c r="N260" t="inlineStr">
@@ -19541,17 +19541,17 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t xml:space="preserve">Højmarksvej 18</t>
+          <t xml:space="preserve">Bækkevej 30</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t xml:space="preserve">6670</t>
+          <t xml:space="preserve">6650</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t xml:space="preserve">5036533</t>
+          <t xml:space="preserve">737370, 5037333</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
@@ -19560,11 +19560,11 @@
         </is>
       </c>
       <c r="J261">
-        <v>2243</v>
+        <v>953</v>
       </c>
       <c r="K261" t="inlineStr">
         <is>
-          <t xml:space="preserve">311894920</t>
+          <t xml:space="preserve">311905030</t>
         </is>
       </c>
       <c r="L261" t="inlineStr">
@@ -19574,7 +19574,7 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-17</t>
+          <t xml:space="preserve">2036-06-01</t>
         </is>
       </c>
       <c r="N261" t="inlineStr">
@@ -19616,30 +19616,30 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t xml:space="preserve">Højmarksvej 18</t>
+          <t xml:space="preserve">Bækkevej 9A</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t xml:space="preserve">6670</t>
+          <t xml:space="preserve">6621</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t xml:space="preserve">5036533</t>
+          <t xml:space="preserve">5020950</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J262">
-        <v>3900</v>
+        <v>1868</v>
       </c>
       <c r="K262" t="inlineStr">
         <is>
-          <t xml:space="preserve">311894909</t>
+          <t xml:space="preserve">311905028</t>
         </is>
       </c>
       <c r="L262" t="inlineStr">
@@ -19649,7 +19649,7 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-17</t>
+          <t xml:space="preserve">2036-06-01</t>
         </is>
       </c>
       <c r="N262" t="inlineStr">
@@ -19691,30 +19691,30 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møllevænget 5</t>
+          <t xml:space="preserve">Lindevej 7A</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t xml:space="preserve">6622</t>
+          <t xml:space="preserve">6682</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t xml:space="preserve">737305, 5019907</t>
+          <t xml:space="preserve">737412, 5037833</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">104</t>
         </is>
       </c>
       <c r="J263">
-        <v>2050</v>
+        <v>1348</v>
       </c>
       <c r="K263" t="inlineStr">
         <is>
-          <t xml:space="preserve">311894926</t>
+          <t xml:space="preserve">311914611</t>
         </is>
       </c>
       <c r="L263" t="inlineStr">
@@ -19724,7 +19724,7 @@
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-17</t>
+          <t xml:space="preserve">2036-06-01</t>
         </is>
       </c>
       <c r="N263" t="inlineStr">
@@ -19766,30 +19766,30 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ørstedvej 10</t>
+          <t xml:space="preserve">Lindevej 7C</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t xml:space="preserve">6630</t>
+          <t xml:space="preserve">6682</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t xml:space="preserve">737335, 5186260</t>
+          <t xml:space="preserve">5037833</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">101</t>
         </is>
       </c>
       <c r="J264">
-        <v>537</v>
+        <v>96</v>
       </c>
       <c r="K264" t="inlineStr">
         <is>
-          <t xml:space="preserve">311894879</t>
+          <t xml:space="preserve">311905034</t>
         </is>
       </c>
       <c r="L264" t="inlineStr">
@@ -19799,7 +19799,7 @@
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-17</t>
+          <t xml:space="preserve">2036-06-01</t>
         </is>
       </c>
       <c r="N264" t="inlineStr">
@@ -19841,30 +19841,30 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionvej 2A</t>
+          <t xml:space="preserve">Holleskovvej 4</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t xml:space="preserve">6752</t>
+          <t xml:space="preserve">6683</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t xml:space="preserve">737383, 5045451</t>
+          <t xml:space="preserve">737386, 5034767</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J265">
-        <v>423</v>
+        <v>452</v>
       </c>
       <c r="K265" t="inlineStr">
         <is>
-          <t xml:space="preserve">311895815</t>
+          <t xml:space="preserve">311905606</t>
         </is>
       </c>
       <c r="L265" t="inlineStr">
@@ -19874,7 +19874,7 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-22</t>
+          <t xml:space="preserve">2036-06-04</t>
         </is>
       </c>
       <c r="N265" t="inlineStr">
@@ -19916,30 +19916,30 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionvej 2A</t>
+          <t xml:space="preserve">Skolegade 1</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t xml:space="preserve">6752</t>
+          <t xml:space="preserve">6630</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t xml:space="preserve">737383, 5045451</t>
+          <t xml:space="preserve">5195366</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J266">
-        <v>1665</v>
+        <v>1052</v>
       </c>
       <c r="K266" t="inlineStr">
         <is>
-          <t xml:space="preserve">311896169</t>
+          <t xml:space="preserve">311905369</t>
         </is>
       </c>
       <c r="L266" t="inlineStr">
@@ -19949,7 +19949,7 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-23</t>
+          <t xml:space="preserve">2036-06-04</t>
         </is>
       </c>
       <c r="N266" t="inlineStr">
@@ -19991,30 +19991,30 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionvej 2A</t>
+          <t xml:space="preserve">Søndergyden 17</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t xml:space="preserve">6752</t>
+          <t xml:space="preserve">6630</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t xml:space="preserve">737383, 5045451</t>
+          <t xml:space="preserve">9196089</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J267">
-        <v>273</v>
+        <v>1782</v>
       </c>
       <c r="K267" t="inlineStr">
         <is>
-          <t xml:space="preserve">311896606</t>
+          <t xml:space="preserve">311905611</t>
         </is>
       </c>
       <c r="L267" t="inlineStr">
@@ -20024,7 +20024,7 @@
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-24</t>
+          <t xml:space="preserve">2036-06-04</t>
         </is>
       </c>
       <c r="N267" t="inlineStr">
@@ -20066,7 +20066,7 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bækkevej 30</t>
+          <t xml:space="preserve">Byagervej 3</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
@@ -20076,20 +20076,20 @@
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t xml:space="preserve">737370, 5037333</t>
+          <t xml:space="preserve">737365, 5032515</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J268">
-        <v>953</v>
+        <v>2937</v>
       </c>
       <c r="K268" t="inlineStr">
         <is>
-          <t xml:space="preserve">311905030</t>
+          <t xml:space="preserve">311907452</t>
         </is>
       </c>
       <c r="L268" t="inlineStr">
@@ -20099,7 +20099,7 @@
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-06-01</t>
+          <t xml:space="preserve">2036-06-11</t>
         </is>
       </c>
       <c r="N268" t="inlineStr">
@@ -20141,17 +20141,17 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bækkevej 9A</t>
+          <t xml:space="preserve">Petersmindevej 1</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t xml:space="preserve">6621</t>
+          <t xml:space="preserve">6600</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t xml:space="preserve">5020950</t>
+          <t xml:space="preserve">7955800</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
@@ -20160,11 +20160,11 @@
         </is>
       </c>
       <c r="J269">
-        <v>1868</v>
+        <v>6676</v>
       </c>
       <c r="K269" t="inlineStr">
         <is>
-          <t xml:space="preserve">311905028</t>
+          <t xml:space="preserve">311915214</t>
         </is>
       </c>
       <c r="L269" t="inlineStr">
@@ -20174,7 +20174,7 @@
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-06-01</t>
+          <t xml:space="preserve">2036-07-20</t>
         </is>
       </c>
       <c r="N269" t="inlineStr">
@@ -20216,30 +20216,30 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lindevej 7A</t>
+          <t xml:space="preserve">Petersmindevej 1</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t xml:space="preserve">6682</t>
+          <t xml:space="preserve">6600</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t xml:space="preserve">737412, 5037833</t>
+          <t xml:space="preserve">7955800</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t xml:space="preserve">104</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J270">
-        <v>1348</v>
+        <v>2183</v>
       </c>
       <c r="K270" t="inlineStr">
         <is>
-          <t xml:space="preserve">311914611</t>
+          <t xml:space="preserve">311915210</t>
         </is>
       </c>
       <c r="L270" t="inlineStr">
@@ -20249,7 +20249,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-06-01</t>
+          <t xml:space="preserve">2036-07-20</t>
         </is>
       </c>
       <c r="N270" t="inlineStr">
@@ -20291,30 +20291,30 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lindevej 7C</t>
+          <t xml:space="preserve">Petersmindevej 1</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t xml:space="preserve">6682</t>
+          <t xml:space="preserve">6600</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t xml:space="preserve">5037833</t>
+          <t xml:space="preserve">7955800</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t xml:space="preserve">101</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J271">
-        <v>96</v>
+        <v>310</v>
       </c>
       <c r="K271" t="inlineStr">
         <is>
-          <t xml:space="preserve">311905034</t>
+          <t xml:space="preserve">311915206</t>
         </is>
       </c>
       <c r="L271" t="inlineStr">
@@ -20324,7 +20324,7 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-06-01</t>
+          <t xml:space="preserve">2036-07-20</t>
         </is>
       </c>
       <c r="N271" t="inlineStr">
@@ -20366,30 +20366,30 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holleskovvej 4</t>
+          <t xml:space="preserve">Petersmindevej 1</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t xml:space="preserve">6683</t>
+          <t xml:space="preserve">6600</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t xml:space="preserve">737386, 5034767</t>
+          <t xml:space="preserve">7955800</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J272">
-        <v>452</v>
+        <v>907</v>
       </c>
       <c r="K272" t="inlineStr">
         <is>
-          <t xml:space="preserve">311905606</t>
+          <t xml:space="preserve">311915205</t>
         </is>
       </c>
       <c r="L272" t="inlineStr">
@@ -20399,7 +20399,7 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-06-04</t>
+          <t xml:space="preserve">2036-07-20</t>
         </is>
       </c>
       <c r="N272" t="inlineStr">
@@ -20441,30 +20441,30 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 1</t>
+          <t xml:space="preserve">Petersmindevej 1</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t xml:space="preserve">6630</t>
+          <t xml:space="preserve">6600</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t xml:space="preserve">5195366</t>
+          <t xml:space="preserve">7955800</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J273">
-        <v>1052</v>
+        <v>1135</v>
       </c>
       <c r="K273" t="inlineStr">
         <is>
-          <t xml:space="preserve">311905369</t>
+          <t xml:space="preserve">311915208</t>
         </is>
       </c>
       <c r="L273" t="inlineStr">
@@ -20474,7 +20474,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-06-04</t>
+          <t xml:space="preserve">2036-07-20</t>
         </is>
       </c>
       <c r="N273" t="inlineStr">
@@ -20516,30 +20516,30 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndergyden 17</t>
+          <t xml:space="preserve">Petersmindevej 1</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t xml:space="preserve">6630</t>
+          <t xml:space="preserve">6600</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t xml:space="preserve">9196089</t>
+          <t xml:space="preserve">7955800</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J274">
-        <v>1782</v>
+        <v>1397</v>
       </c>
       <c r="K274" t="inlineStr">
         <is>
-          <t xml:space="preserve">311905611</t>
+          <t xml:space="preserve">311915207</t>
         </is>
       </c>
       <c r="L274" t="inlineStr">
@@ -20549,7 +20549,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-06-04</t>
+          <t xml:space="preserve">2036-07-20</t>
         </is>
       </c>
       <c r="N274" t="inlineStr">
@@ -20591,30 +20591,30 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t xml:space="preserve">Byagervej 3</t>
+          <t xml:space="preserve">Ørstedvej 10</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t xml:space="preserve">6650</t>
+          <t xml:space="preserve">6630</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t xml:space="preserve">737365, 5032515</t>
+          <t xml:space="preserve">737335, 5186260</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J275">
-        <v>2937</v>
+        <v>244</v>
       </c>
       <c r="K275" t="inlineStr">
         <is>
-          <t xml:space="preserve">311907452</t>
+          <t xml:space="preserve">311916957</t>
         </is>
       </c>
       <c r="L275" t="inlineStr">
@@ -20624,7 +20624,7 @@
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-06-11</t>
+          <t xml:space="preserve">2036-08-03</t>
         </is>
       </c>
       <c r="N275" t="inlineStr">
@@ -20666,7 +20666,7 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t xml:space="preserve">Petersmindevej 1</t>
+          <t xml:space="preserve">Petersmindevej 2A</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
@@ -20676,30 +20676,30 @@
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t xml:space="preserve">7955800</t>
+          <t xml:space="preserve">9203884</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">100</t>
         </is>
       </c>
       <c r="J276">
-        <v>6676</v>
+        <v>1872</v>
       </c>
       <c r="K276" t="inlineStr">
         <is>
-          <t xml:space="preserve">311915214</t>
+          <t xml:space="preserve">311922670</t>
         </is>
       </c>
       <c r="L276" t="inlineStr">
         <is>
-          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+          <t xml:space="preserve">Norca Aps</t>
         </is>
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-07-20</t>
+          <t xml:space="preserve">2036-08-31</t>
         </is>
       </c>
       <c r="N276" t="inlineStr">
@@ -20741,30 +20741,30 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t xml:space="preserve">Petersmindevej 1</t>
+          <t xml:space="preserve">Lille Veumvej 6</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t xml:space="preserve">6600</t>
+          <t xml:space="preserve">6650</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t xml:space="preserve">7955800</t>
+          <t xml:space="preserve">5031183</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J277">
-        <v>2183</v>
+        <v>1056</v>
       </c>
       <c r="K277" t="inlineStr">
         <is>
-          <t xml:space="preserve">311915210</t>
+          <t xml:space="preserve">311923191</t>
         </is>
       </c>
       <c r="L277" t="inlineStr">
@@ -20774,7 +20774,7 @@
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-07-20</t>
+          <t xml:space="preserve">2036-09-02</t>
         </is>
       </c>
       <c r="N277" t="inlineStr">
@@ -20816,7 +20816,7 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t xml:space="preserve">Petersmindevej 1</t>
+          <t xml:space="preserve">Ø. Skibelundvej 15</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
@@ -20826,20 +20826,20 @@
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t xml:space="preserve">7955800</t>
+          <t xml:space="preserve">5039005</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J278">
-        <v>310</v>
+        <v>326</v>
       </c>
       <c r="K278" t="inlineStr">
         <is>
-          <t xml:space="preserve">311915206</t>
+          <t xml:space="preserve">311923198</t>
         </is>
       </c>
       <c r="L278" t="inlineStr">
@@ -20849,7 +20849,7 @@
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-07-20</t>
+          <t xml:space="preserve">2036-09-02</t>
         </is>
       </c>
       <c r="N278" t="inlineStr">
@@ -20891,30 +20891,30 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t xml:space="preserve">Petersmindevej 1</t>
+          <t xml:space="preserve">Stadionvej 6</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t xml:space="preserve">6600</t>
+          <t xml:space="preserve">6650</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t xml:space="preserve">7955800</t>
+          <t xml:space="preserve">5032443</t>
         </is>
       </c>
       <c r="I279" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J279">
-        <v>907</v>
+        <v>656</v>
       </c>
       <c r="K279" t="inlineStr">
         <is>
-          <t xml:space="preserve">311915205</t>
+          <t xml:space="preserve">311924085</t>
         </is>
       </c>
       <c r="L279" t="inlineStr">
@@ -20924,7 +20924,7 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-07-20</t>
+          <t xml:space="preserve">2036-09-07</t>
         </is>
       </c>
       <c r="N279" t="inlineStr">
@@ -20966,7 +20966,7 @@
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t xml:space="preserve">Petersmindevej 1</t>
+          <t xml:space="preserve">Solhøj 2</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
@@ -20976,20 +20976,20 @@
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t xml:space="preserve">7955800</t>
+          <t xml:space="preserve">5019115</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J280">
-        <v>1135</v>
+        <v>196</v>
       </c>
       <c r="K280" t="inlineStr">
         <is>
-          <t xml:space="preserve">311915208</t>
+          <t xml:space="preserve">311924311</t>
         </is>
       </c>
       <c r="L280" t="inlineStr">
@@ -20999,7 +20999,7 @@
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-07-20</t>
+          <t xml:space="preserve">2036-09-08</t>
         </is>
       </c>
       <c r="N280" t="inlineStr">
@@ -21041,30 +21041,30 @@
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t xml:space="preserve">Petersmindevej 1</t>
+          <t xml:space="preserve">Byagervej 1</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t xml:space="preserve">6600</t>
+          <t xml:space="preserve">6650</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t xml:space="preserve">7955800</t>
+          <t xml:space="preserve">5032515</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J281">
-        <v>1397</v>
+        <v>555</v>
       </c>
       <c r="K281" t="inlineStr">
         <is>
-          <t xml:space="preserve">311915207</t>
+          <t xml:space="preserve">311925241</t>
         </is>
       </c>
       <c r="L281" t="inlineStr">
@@ -21074,7 +21074,7 @@
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-07-20</t>
+          <t xml:space="preserve">2036-09-11</t>
         </is>
       </c>
       <c r="N281" t="inlineStr">
@@ -21116,30 +21116,30 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ørstedvej 10</t>
+          <t xml:space="preserve">Lindevej 5</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t xml:space="preserve">6630</t>
+          <t xml:space="preserve">6682</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t xml:space="preserve">737335, 5186260</t>
+          <t xml:space="preserve">5037833</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J282">
-        <v>244</v>
+        <v>443</v>
       </c>
       <c r="K282" t="inlineStr">
         <is>
-          <t xml:space="preserve">311916957</t>
+          <t xml:space="preserve">311925148</t>
         </is>
       </c>
       <c r="L282" t="inlineStr">
@@ -21149,7 +21149,7 @@
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-08-03</t>
+          <t xml:space="preserve">2036-09-11</t>
         </is>
       </c>
       <c r="N282" t="inlineStr">
@@ -21191,40 +21191,40 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t xml:space="preserve">Petersmindevej 2A</t>
+          <t xml:space="preserve">Lindevej 5</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t xml:space="preserve">6600</t>
+          <t xml:space="preserve">6682</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t xml:space="preserve">9203884</t>
+          <t xml:space="preserve">5037833</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t xml:space="preserve">100</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J283">
-        <v>1872</v>
+        <v>169</v>
       </c>
       <c r="K283" t="inlineStr">
         <is>
-          <t xml:space="preserve">311922670</t>
+          <t xml:space="preserve">311925146</t>
         </is>
       </c>
       <c r="L283" t="inlineStr">
         <is>
-          <t xml:space="preserve">Norca Aps</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-08-31</t>
+          <t xml:space="preserve">2036-09-11</t>
         </is>
       </c>
       <c r="N283" t="inlineStr">
@@ -21266,30 +21266,30 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lille Veumvej 6</t>
+          <t xml:space="preserve">Lindevej 7B</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t xml:space="preserve">6650</t>
+          <t xml:space="preserve">6682</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t xml:space="preserve">5031183</t>
+          <t xml:space="preserve">5037833</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">201</t>
         </is>
       </c>
       <c r="J284">
-        <v>1056</v>
+        <v>118</v>
       </c>
       <c r="K284" t="inlineStr">
         <is>
-          <t xml:space="preserve">311923191</t>
+          <t xml:space="preserve">311925144</t>
         </is>
       </c>
       <c r="L284" t="inlineStr">
@@ -21299,7 +21299,7 @@
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-09-02</t>
+          <t xml:space="preserve">2036-09-11</t>
         </is>
       </c>
       <c r="N284" t="inlineStr">
@@ -21341,17 +21341,17 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ø. Skibelundvej 15</t>
+          <t xml:space="preserve">Dixensvej 1A</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t xml:space="preserve">6600</t>
+          <t xml:space="preserve">6630</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t xml:space="preserve">5039005</t>
+          <t xml:space="preserve">5185767</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
@@ -21360,11 +21360,11 @@
         </is>
       </c>
       <c r="J285">
-        <v>326</v>
+        <v>765</v>
       </c>
       <c r="K285" t="inlineStr">
         <is>
-          <t xml:space="preserve">311923198</t>
+          <t xml:space="preserve">311925437</t>
         </is>
       </c>
       <c r="L285" t="inlineStr">
@@ -21374,7 +21374,7 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-09-02</t>
+          <t xml:space="preserve">2036-09-14</t>
         </is>
       </c>
       <c r="N285" t="inlineStr">
@@ -21416,17 +21416,17 @@
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionvej 6</t>
+          <t xml:space="preserve">Jels Søndergade 17A</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t xml:space="preserve">6650</t>
+          <t xml:space="preserve">6630</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t xml:space="preserve">5032443</t>
+          <t xml:space="preserve">5185936</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
@@ -21435,11 +21435,11 @@
         </is>
       </c>
       <c r="J286">
-        <v>656</v>
+        <v>270</v>
       </c>
       <c r="K286" t="inlineStr">
         <is>
-          <t xml:space="preserve">311924085</t>
+          <t xml:space="preserve">311926101</t>
         </is>
       </c>
       <c r="L286" t="inlineStr">
@@ -21449,7 +21449,7 @@
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-09-07</t>
+          <t xml:space="preserve">2036-09-16</t>
         </is>
       </c>
       <c r="N286" t="inlineStr">
@@ -21491,7 +21491,7 @@
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t xml:space="preserve">Solhøj 2</t>
+          <t xml:space="preserve">Knudevejen 17A</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
@@ -21501,20 +21501,20 @@
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t xml:space="preserve">5019115</t>
+          <t xml:space="preserve">7813581</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J287">
-        <v>196</v>
+        <v>386</v>
       </c>
       <c r="K287" t="inlineStr">
         <is>
-          <t xml:space="preserve">311924311</t>
+          <t xml:space="preserve">311926710</t>
         </is>
       </c>
       <c r="L287" t="inlineStr">
@@ -21524,7 +21524,7 @@
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-09-08</t>
+          <t xml:space="preserve">2036-09-18</t>
         </is>
       </c>
       <c r="N287" t="inlineStr">
@@ -21566,30 +21566,30 @@
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t xml:space="preserve">Byagervej 1</t>
+          <t xml:space="preserve">Knudevejen 17B</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t xml:space="preserve">6650</t>
+          <t xml:space="preserve">6600</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t xml:space="preserve">5032515</t>
+          <t xml:space="preserve">7813581</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J288">
-        <v>555</v>
+        <v>386</v>
       </c>
       <c r="K288" t="inlineStr">
         <is>
-          <t xml:space="preserve">311925241</t>
+          <t xml:space="preserve">311926704</t>
         </is>
       </c>
       <c r="L288" t="inlineStr">
@@ -21599,7 +21599,7 @@
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-09-11</t>
+          <t xml:space="preserve">2036-09-18</t>
         </is>
       </c>
       <c r="N288" t="inlineStr">
@@ -21641,30 +21641,30 @@
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lindevej 5</t>
+          <t xml:space="preserve">Knudevejen 17B</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t xml:space="preserve">6682</t>
+          <t xml:space="preserve">6600</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t xml:space="preserve">5037833</t>
+          <t xml:space="preserve">7813581</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">61</t>
         </is>
       </c>
       <c r="J289">
-        <v>443</v>
+        <v>130</v>
       </c>
       <c r="K289" t="inlineStr">
         <is>
-          <t xml:space="preserve">311925148</t>
+          <t xml:space="preserve">311926712</t>
         </is>
       </c>
       <c r="L289" t="inlineStr">
@@ -21674,7 +21674,7 @@
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-09-11</t>
+          <t xml:space="preserve">2036-09-18</t>
         </is>
       </c>
       <c r="N289" t="inlineStr">
@@ -21716,30 +21716,30 @@
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lindevej 5</t>
+          <t xml:space="preserve">Hovedgaden 29</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t xml:space="preserve">6682</t>
+          <t xml:space="preserve">6621</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t xml:space="preserve">5037833</t>
+          <t xml:space="preserve">5021457</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J290">
-        <v>169</v>
+        <v>184</v>
       </c>
       <c r="K290" t="inlineStr">
         <is>
-          <t xml:space="preserve">311925146</t>
+          <t xml:space="preserve">311928161</t>
         </is>
       </c>
       <c r="L290" t="inlineStr">
@@ -21749,7 +21749,7 @@
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-09-11</t>
+          <t xml:space="preserve">2036-09-25</t>
         </is>
       </c>
       <c r="N290" t="inlineStr">
@@ -21791,30 +21791,30 @@
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lindevej 7B</t>
+          <t xml:space="preserve">Stadion Alle 2</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t xml:space="preserve">6682</t>
+          <t xml:space="preserve">6621</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t xml:space="preserve">5037833</t>
+          <t xml:space="preserve">5021457</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
         <is>
-          <t xml:space="preserve">201</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J291">
-        <v>118</v>
+        <v>1006</v>
       </c>
       <c r="K291" t="inlineStr">
         <is>
-          <t xml:space="preserve">311925144</t>
+          <t xml:space="preserve">311928157</t>
         </is>
       </c>
       <c r="L291" t="inlineStr">
@@ -21824,7 +21824,7 @@
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-09-11</t>
+          <t xml:space="preserve">2036-09-25</t>
         </is>
       </c>
       <c r="N291" t="inlineStr">
@@ -21866,30 +21866,30 @@
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dixensvej 1A</t>
+          <t xml:space="preserve">Stadion Alle 2</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t xml:space="preserve">6630</t>
+          <t xml:space="preserve">6621</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t xml:space="preserve">5185767</t>
+          <t xml:space="preserve">5021457</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J292">
-        <v>765</v>
+        <v>1360</v>
       </c>
       <c r="K292" t="inlineStr">
         <is>
-          <t xml:space="preserve">311925437</t>
+          <t xml:space="preserve">311928163</t>
         </is>
       </c>
       <c r="L292" t="inlineStr">
@@ -21899,7 +21899,7 @@
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-09-14</t>
+          <t xml:space="preserve">2036-09-25</t>
         </is>
       </c>
       <c r="N292" t="inlineStr">
@@ -21941,30 +21941,30 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jels Søndergade 17A</t>
+          <t xml:space="preserve">Stadion Alle 2</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t xml:space="preserve">6630</t>
+          <t xml:space="preserve">6621</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t xml:space="preserve">5185936</t>
+          <t xml:space="preserve">5021457</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J293">
-        <v>270</v>
+        <v>536</v>
       </c>
       <c r="K293" t="inlineStr">
         <is>
-          <t xml:space="preserve">311926101</t>
+          <t xml:space="preserve">311928160</t>
         </is>
       </c>
       <c r="L293" t="inlineStr">
@@ -21974,7 +21974,7 @@
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-09-16</t>
+          <t xml:space="preserve">2036-09-25</t>
         </is>
       </c>
       <c r="N293" t="inlineStr">
